--- a/excel_files/results_ollamaSharp_laptop.xlsx
+++ b/excel_files/results_ollamaSharp_laptop.xlsx
@@ -588,37 +588,37 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>38</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>5.69</x:v>
+        <x:v>12.59</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>40.2</x:v>
+        <x:v>39.72</x:v>
       </x:c>
       <x:c r="K2" s="0">
-        <x:v>3.33</x:v>
+        <x:v>6.03</x:v>
       </x:c>
       <x:c r="L2" s="0">
-        <x:v>49.23</x:v>
+        <x:v>58.34</x:v>
       </x:c>
       <x:c r="M2" s="0">
-        <x:v>754</x:v>
+        <x:v>1767</x:v>
       </x:c>
       <x:c r="N2" s="0">
-        <x:v>4463</x:v>
+        <x:v>5913</x:v>
       </x:c>
       <x:c r="O2" s="0">
-        <x:v>3801</x:v>
+        <x:v>4869</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>73</x:v>
       </x:c>
       <x:c r="R2" s="0">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="S2" s="0">
         <x:v>628</x:v>
@@ -627,16 +627,16 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="U2" s="0">
-        <x:v>782</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="V2" s="0">
-        <x:v>74</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="W2" s="0">
-        <x:v>3602</x:v>
+        <x:v>5052</x:v>
       </x:c>
       <x:c r="X2" s="0">
-        <x:v>2950</x:v>
+        <x:v>4026</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:24">
@@ -653,55 +653,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>65</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>2.43</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>34.36</x:v>
+        <x:v>33.61</x:v>
       </x:c>
       <x:c r="K3" s="0">
-        <x:v>5.78</x:v>
+        <x:v>4.04</x:v>
       </x:c>
       <x:c r="L3" s="0">
-        <x:v>42.57</x:v>
+        <x:v>40.33</x:v>
       </x:c>
       <x:c r="M3" s="0">
-        <x:v>4464</x:v>
+        <x:v>5915</x:v>
       </x:c>
       <x:c r="N3" s="0">
-        <x:v>4474</x:v>
+        <x:v>5921</x:v>
       </x:c>
       <x:c r="O3" s="0">
-        <x:v>4469</x:v>
+        <x:v>5917</x:v>
       </x:c>
       <x:c r="P3" s="0">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="Q3" s="0">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="R3" s="0">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="Q3" s="0">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="R3" s="0">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="S3" s="0">
-        <x:v>788</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="T3" s="0">
-        <x:v>789</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="U3" s="0">
-        <x:v>789</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="V3" s="0">
-        <x:v>3602</x:v>
+        <x:v>5051</x:v>
       </x:c>
       <x:c r="W3" s="0">
-        <x:v>3609</x:v>
+        <x:v>5057</x:v>
       </x:c>
       <x:c r="X3" s="0">
-        <x:v>3605</x:v>
+        <x:v>5055</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:24">
@@ -718,40 +718,40 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>93</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2.44</x:v>
+        <x:v>2.77</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>33.22</x:v>
+        <x:v>32.83</x:v>
       </x:c>
       <x:c r="K4" s="0">
-        <x:v>8.75</x:v>
+        <x:v>6.29</x:v>
       </x:c>
       <x:c r="L4" s="0">
-        <x:v>44.4</x:v>
+        <x:v>41.89</x:v>
       </x:c>
       <x:c r="M4" s="0">
-        <x:v>4474</x:v>
+        <x:v>5604</x:v>
       </x:c>
       <x:c r="N4" s="0">
-        <x:v>4478</x:v>
+        <x:v>5928</x:v>
       </x:c>
       <x:c r="O4" s="0">
-        <x:v>4476</x:v>
+        <x:v>5882</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="R4" s="0">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="S4" s="0">
-        <x:v>790</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="T4" s="0">
         <x:v>792</x:v>
@@ -760,13 +760,13 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="V4" s="0">
-        <x:v>3608</x:v>
+        <x:v>4738</x:v>
       </x:c>
       <x:c r="W4" s="0">
-        <x:v>3610</x:v>
+        <x:v>5061</x:v>
       </x:c>
       <x:c r="X4" s="0">
-        <x:v>3609</x:v>
+        <x:v>5017</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:24">
@@ -783,55 +783,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>20</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.76</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>31.7</x:v>
+        <x:v>29.78</x:v>
       </x:c>
       <x:c r="K5" s="0">
-        <x:v>1.84</x:v>
+        <x:v>3.91</x:v>
       </x:c>
       <x:c r="L5" s="0">
-        <x:v>36.3</x:v>
+        <x:v>36.5</x:v>
       </x:c>
       <x:c r="M5" s="0">
-        <x:v>4383</x:v>
+        <x:v>5318</x:v>
       </x:c>
       <x:c r="N5" s="0">
-        <x:v>4483</x:v>
+        <x:v>5586</x:v>
       </x:c>
       <x:c r="O5" s="0">
-        <x:v>4481</x:v>
+        <x:v>5352</x:v>
       </x:c>
       <x:c r="P5" s="0">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="Q5" s="0">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="Q5" s="0">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="R5" s="0">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="S5" s="0">
         <x:v>793</x:v>
       </x:c>
       <x:c r="T5" s="0">
-        <x:v>794</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="U5" s="0">
-        <x:v>794</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="V5" s="0">
-        <x:v>3513</x:v>
+        <x:v>4450</x:v>
       </x:c>
       <x:c r="W5" s="0">
-        <x:v>3613</x:v>
+        <x:v>4718</x:v>
       </x:c>
       <x:c r="X5" s="0">
-        <x:v>3611</x:v>
+        <x:v>4483</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:24">
@@ -851,34 +851,34 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>2.69</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>33.59</x:v>
+        <x:v>31.88</x:v>
       </x:c>
       <x:c r="K6" s="0">
-        <x:v>0.53</x:v>
+        <x:v>0.47</x:v>
       </x:c>
       <x:c r="L6" s="0">
-        <x:v>36.81</x:v>
+        <x:v>35.14</x:v>
       </x:c>
       <x:c r="M6" s="0">
-        <x:v>4486</x:v>
+        <x:v>5324</x:v>
       </x:c>
       <x:c r="N6" s="0">
-        <x:v>4491</x:v>
+        <x:v>5329</x:v>
       </x:c>
       <x:c r="O6" s="0">
-        <x:v>4487</x:v>
+        <x:v>5324</x:v>
       </x:c>
       <x:c r="P6" s="0">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="Q6" s="0">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="R6" s="0">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="Q6" s="0">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="R6" s="0">
-        <x:v>76</x:v>
       </x:c>
       <x:c r="S6" s="0">
         <x:v>795</x:v>
@@ -890,13 +890,13 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="V6" s="0">
-        <x:v>3614</x:v>
+        <x:v>4453</x:v>
       </x:c>
       <x:c r="W6" s="0">
-        <x:v>3618</x:v>
+        <x:v>4456</x:v>
       </x:c>
       <x:c r="X6" s="0">
-        <x:v>3615</x:v>
+        <x:v>4453</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:24">
@@ -913,34 +913,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>86</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G7" s="0">
         <x:v>2.64</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>35.77</x:v>
+        <x:v>33.44</x:v>
       </x:c>
       <x:c r="K7" s="0">
-        <x:v>8.26</x:v>
+        <x:v>19.05</x:v>
       </x:c>
       <x:c r="L7" s="0">
-        <x:v>46.67</x:v>
+        <x:v>55.13</x:v>
       </x:c>
       <x:c r="M7" s="0">
-        <x:v>4435</x:v>
+        <x:v>5329</x:v>
       </x:c>
       <x:c r="N7" s="0">
-        <x:v>4496</x:v>
+        <x:v>5335</x:v>
       </x:c>
       <x:c r="O7" s="0">
-        <x:v>4494</x:v>
+        <x:v>5333</x:v>
       </x:c>
       <x:c r="P7" s="0">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="Q7" s="0">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="Q7" s="0">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="R7" s="0">
         <x:v>76</x:v>
@@ -949,19 +949,19 @@
         <x:v>798</x:v>
       </x:c>
       <x:c r="T7" s="0">
-        <x:v>800</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="U7" s="0">
-        <x:v>800</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="V7" s="0">
-        <x:v>3558</x:v>
+        <x:v>4456</x:v>
       </x:c>
       <x:c r="W7" s="0">
-        <x:v>3620</x:v>
+        <x:v>4460</x:v>
       </x:c>
       <x:c r="X7" s="0">
-        <x:v>3618</x:v>
+        <x:v>4458</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:24">
@@ -978,34 +978,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>240</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>3.37</x:v>
+        <x:v>2.82</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>35.32</x:v>
+        <x:v>33.65</x:v>
       </x:c>
       <x:c r="K8" s="0">
-        <x:v>23.58</x:v>
+        <x:v>24.74</x:v>
       </x:c>
       <x:c r="L8" s="0">
-        <x:v>62.27</x:v>
+        <x:v>61.2</x:v>
       </x:c>
       <x:c r="M8" s="0">
-        <x:v>4497</x:v>
+        <x:v>5338</x:v>
       </x:c>
       <x:c r="N8" s="0">
-        <x:v>4505</x:v>
+        <x:v>5346</x:v>
       </x:c>
       <x:c r="O8" s="0">
-        <x:v>4499</x:v>
+        <x:v>5340</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R8" s="0">
         <x:v>77</x:v>
@@ -1020,13 +1020,13 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="V8" s="0">
-        <x:v>3620</x:v>
+        <x:v>4460</x:v>
       </x:c>
       <x:c r="W8" s="0">
-        <x:v>3624</x:v>
+        <x:v>4464</x:v>
       </x:c>
       <x:c r="X8" s="0">
-        <x:v>3621</x:v>
+        <x:v>4462</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:24">
@@ -1043,37 +1043,37 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>102</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2.76</x:v>
+        <x:v>2.68</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>35.08</x:v>
+        <x:v>33.08</x:v>
       </x:c>
       <x:c r="K9" s="0">
-        <x:v>9.85</x:v>
+        <x:v>3.91</x:v>
       </x:c>
       <x:c r="L9" s="0">
-        <x:v>47.7</x:v>
+        <x:v>39.67</x:v>
       </x:c>
       <x:c r="M9" s="0">
-        <x:v>4501</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="N9" s="0">
-        <x:v>4512</x:v>
+        <x:v>6354</x:v>
       </x:c>
       <x:c r="O9" s="0">
-        <x:v>4503</x:v>
+        <x:v>6076</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="Q9" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="R9" s="0">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="S9" s="0">
         <x:v>802</x:v>
@@ -1085,13 +1085,13 @@
         <x:v>803</x:v>
       </x:c>
       <x:c r="V9" s="0">
-        <x:v>3622</x:v>
+        <x:v>4463</x:v>
       </x:c>
       <x:c r="W9" s="0">
-        <x:v>3627</x:v>
+        <x:v>5473</x:v>
       </x:c>
       <x:c r="X9" s="0">
-        <x:v>3623</x:v>
+        <x:v>5195</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:24">
@@ -1108,28 +1108,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>63</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>2.79</x:v>
+        <x:v>2.77</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>34.73</x:v>
+        <x:v>33.03</x:v>
       </x:c>
       <x:c r="K10" s="0">
-        <x:v>6.25</x:v>
+        <x:v>8.63</x:v>
       </x:c>
       <x:c r="L10" s="0">
-        <x:v>43.78</x:v>
+        <x:v>44.43</x:v>
       </x:c>
       <x:c r="M10" s="0">
-        <x:v>4505</x:v>
+        <x:v>6349</x:v>
       </x:c>
       <x:c r="N10" s="0">
-        <x:v>4508</x:v>
+        <x:v>6358</x:v>
       </x:c>
       <x:c r="O10" s="0">
-        <x:v>4506</x:v>
+        <x:v>6356</x:v>
       </x:c>
       <x:c r="P10" s="0">
         <x:v>77</x:v>
@@ -1150,13 +1150,13 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="V10" s="0">
-        <x:v>3624</x:v>
+        <x:v>5466</x:v>
       </x:c>
       <x:c r="W10" s="0">
-        <x:v>3625</x:v>
+        <x:v>5475</x:v>
       </x:c>
       <x:c r="X10" s="0">
-        <x:v>3624</x:v>
+        <x:v>5474</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:24">
@@ -1173,28 +1173,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>78</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>2.67</x:v>
+        <x:v>2.71</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>34.71</x:v>
+        <x:v>32.96</x:v>
       </x:c>
       <x:c r="K11" s="0">
-        <x:v>7.77</x:v>
+        <x:v>7.42</x:v>
       </x:c>
       <x:c r="L11" s="0">
-        <x:v>45.15</x:v>
+        <x:v>43.09</x:v>
       </x:c>
       <x:c r="M11" s="0">
-        <x:v>4510</x:v>
+        <x:v>6361</x:v>
       </x:c>
       <x:c r="N11" s="0">
-        <x:v>4515</x:v>
+        <x:v>6365</x:v>
       </x:c>
       <x:c r="O11" s="0">
-        <x:v>4512</x:v>
+        <x:v>6362</x:v>
       </x:c>
       <x:c r="P11" s="0">
         <x:v>77</x:v>
@@ -1203,7 +1203,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="R11" s="0">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="S11" s="0">
         <x:v>806</x:v>
@@ -1215,13 +1215,13 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="V11" s="0">
-        <x:v>3626</x:v>
+        <x:v>5476</x:v>
       </x:c>
       <x:c r="W11" s="0">
-        <x:v>3629</x:v>
+        <x:v>5478</x:v>
       </x:c>
       <x:c r="X11" s="0">
-        <x:v>3627</x:v>
+        <x:v>5477</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:24">
@@ -1238,31 +1238,31 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>37</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2.78</x:v>
+        <x:v>2.68</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>35.43</x:v>
+        <x:v>33.4</x:v>
       </x:c>
       <x:c r="K12" s="0">
-        <x:v>4.06</x:v>
+        <x:v>18.13</x:v>
       </x:c>
       <x:c r="L12" s="0">
-        <x:v>42.26</x:v>
+        <x:v>54.21</x:v>
       </x:c>
       <x:c r="M12" s="0">
-        <x:v>4516</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="N12" s="0">
-        <x:v>4521</x:v>
+        <x:v>6372</x:v>
       </x:c>
       <x:c r="O12" s="0">
-        <x:v>4517</x:v>
+        <x:v>5817</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="Q12" s="0">
         <x:v>80</x:v>
@@ -1271,22 +1271,22 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="S12" s="0">
-        <x:v>808</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="T12" s="0">
-        <x:v>809</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="U12" s="0">
-        <x:v>809</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="V12" s="0">
-        <x:v>3629</x:v>
+        <x:v>4713</x:v>
       </x:c>
       <x:c r="W12" s="0">
-        <x:v>3632</x:v>
+        <x:v>5482</x:v>
       </x:c>
       <x:c r="X12" s="0">
-        <x:v>3630</x:v>
+        <x:v>4929</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:24">
@@ -1303,55 +1303,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>482</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>2.81</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>31.06</x:v>
+        <x:v>28.97</x:v>
       </x:c>
       <x:c r="K13" s="0">
-        <x:v>52.49</x:v>
+        <x:v>22.66</x:v>
       </x:c>
       <x:c r="L13" s="0">
-        <x:v>86.37</x:v>
+        <x:v>54.47</x:v>
       </x:c>
       <x:c r="M13" s="0">
-        <x:v>4518</x:v>
+        <x:v>5603</x:v>
       </x:c>
       <x:c r="N13" s="0">
-        <x:v>4522</x:v>
+        <x:v>5608</x:v>
       </x:c>
       <x:c r="O13" s="0">
-        <x:v>4521</x:v>
+        <x:v>5606</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="R13" s="0">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="S13" s="0">
-        <x:v>810</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="T13" s="0">
-        <x:v>812</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="U13" s="0">
-        <x:v>812</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="V13" s="0">
-        <x:v>3631</x:v>
+        <x:v>4714</x:v>
       </x:c>
       <x:c r="W13" s="0">
-        <x:v>3632</x:v>
+        <x:v>4718</x:v>
       </x:c>
       <x:c r="X13" s="0">
-        <x:v>3632</x:v>
+        <x:v>4716</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:24">
@@ -1368,31 +1368,31 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.82</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>29.67</x:v>
+        <x:v>28.17</x:v>
       </x:c>
       <x:c r="K14" s="0">
-        <x:v>0.48</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="L14" s="0">
-        <x:v>32.87</x:v>
+        <x:v>33.19</x:v>
       </x:c>
       <x:c r="M14" s="0">
-        <x:v>4524</x:v>
+        <x:v>5610</x:v>
       </x:c>
       <x:c r="N14" s="0">
-        <x:v>4532</x:v>
+        <x:v>5617</x:v>
       </x:c>
       <x:c r="O14" s="0">
-        <x:v>4526</x:v>
+        <x:v>5611</x:v>
       </x:c>
       <x:c r="P14" s="0">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="Q14" s="0">
         <x:v>81</x:v>
@@ -1401,22 +1401,22 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="S14" s="0">
-        <x:v>813</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="T14" s="0">
-        <x:v>814</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="U14" s="0">
-        <x:v>814</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="V14" s="0">
-        <x:v>3633</x:v>
+        <x:v>4717</x:v>
       </x:c>
       <x:c r="W14" s="0">
-        <x:v>3637</x:v>
+        <x:v>4721</x:v>
       </x:c>
       <x:c r="X14" s="0">
-        <x:v>3633</x:v>
+        <x:v>4718</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:24">
@@ -1433,55 +1433,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>108</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2.83</x:v>
+        <x:v>2.69</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>34.74</x:v>
+        <x:v>33.35</x:v>
       </x:c>
       <x:c r="K15" s="0">
-        <x:v>10.63</x:v>
+        <x:v>5.73</x:v>
       </x:c>
       <x:c r="L15" s="0">
-        <x:v>48.2</x:v>
+        <x:v>41.76</x:v>
       </x:c>
       <x:c r="M15" s="0">
-        <x:v>4529</x:v>
+        <x:v>5596</x:v>
       </x:c>
       <x:c r="N15" s="0">
-        <x:v>4533</x:v>
+        <x:v>5617</x:v>
       </x:c>
       <x:c r="O15" s="0">
-        <x:v>4530</x:v>
+        <x:v>5598</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="Q15" s="0">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="R15" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="S15" s="0">
-        <x:v>815</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="T15" s="0">
-        <x:v>816</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="U15" s="0">
-        <x:v>816</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="V15" s="0">
-        <x:v>3635</x:v>
+        <x:v>4701</x:v>
       </x:c>
       <x:c r="W15" s="0">
-        <x:v>3637</x:v>
+        <x:v>4721</x:v>
       </x:c>
       <x:c r="X15" s="0">
-        <x:v>3636</x:v>
+        <x:v>4703</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:24">
@@ -1498,31 +1498,31 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>273</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>2.76</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>38.17</x:v>
+        <x:v>36.36</x:v>
       </x:c>
       <x:c r="K16" s="0">
-        <x:v>26.9</x:v>
+        <x:v>38.77</x:v>
       </x:c>
       <x:c r="L16" s="0">
-        <x:v>67.83</x:v>
+        <x:v>77.93</x:v>
       </x:c>
       <x:c r="M16" s="0">
-        <x:v>4515</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="N16" s="0">
-        <x:v>4538</x:v>
+        <x:v>5604</x:v>
       </x:c>
       <x:c r="O16" s="0">
-        <x:v>4528</x:v>
+        <x:v>5602</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>80</x:v>
@@ -1540,13 +1540,13 @@
         <x:v>819</x:v>
       </x:c>
       <x:c r="V16" s="0">
-        <x:v>3619</x:v>
+        <x:v>4703</x:v>
       </x:c>
       <x:c r="W16" s="0">
-        <x:v>3639</x:v>
+        <x:v>4706</x:v>
       </x:c>
       <x:c r="X16" s="0">
-        <x:v>3631</x:v>
+        <x:v>4704</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:24">
@@ -1563,34 +1563,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>334</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>34.16</x:v>
+        <x:v>32.64</x:v>
       </x:c>
       <x:c r="K17" s="0">
-        <x:v>33.14</x:v>
+        <x:v>10.26</x:v>
       </x:c>
       <x:c r="L17" s="0">
-        <x:v>70.02</x:v>
+        <x:v>45.6</x:v>
       </x:c>
       <x:c r="M17" s="0">
-        <x:v>4519</x:v>
+        <x:v>5601</x:v>
       </x:c>
       <x:c r="N17" s="0">
-        <x:v>4529</x:v>
+        <x:v>5615</x:v>
       </x:c>
       <x:c r="O17" s="0">
-        <x:v>4521</x:v>
+        <x:v>5603</x:v>
       </x:c>
       <x:c r="P17" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="R17" s="0">
         <x:v>79</x:v>
@@ -1605,13 +1605,13 @@
         <x:v>821</x:v>
       </x:c>
       <x:c r="V17" s="0">
-        <x:v>3620</x:v>
+        <x:v>4701</x:v>
       </x:c>
       <x:c r="W17" s="0">
-        <x:v>3625</x:v>
+        <x:v>4710</x:v>
       </x:c>
       <x:c r="X17" s="0">
-        <x:v>3622</x:v>
+        <x:v>4703</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:24">
@@ -1628,34 +1628,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G18" s="0">
         <x:v>2.74</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>35.31</x:v>
+        <x:v>34.24</x:v>
       </x:c>
       <x:c r="K18" s="0">
-        <x:v>4.23</x:v>
+        <x:v>4.61</x:v>
       </x:c>
       <x:c r="L18" s="0">
-        <x:v>42.28</x:v>
+        <x:v>41.6</x:v>
       </x:c>
       <x:c r="M18" s="0">
-        <x:v>4520</x:v>
+        <x:v>5604</x:v>
       </x:c>
       <x:c r="N18" s="0">
-        <x:v>4524</x:v>
+        <x:v>6866</x:v>
       </x:c>
       <x:c r="O18" s="0">
-        <x:v>4523</x:v>
+        <x:v>6263</x:v>
       </x:c>
       <x:c r="P18" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="Q18" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="R18" s="0">
         <x:v>78</x:v>
@@ -1670,13 +1670,13 @@
         <x:v>824</x:v>
       </x:c>
       <x:c r="V18" s="0">
-        <x:v>3619</x:v>
+        <x:v>4703</x:v>
       </x:c>
       <x:c r="W18" s="0">
-        <x:v>3623</x:v>
+        <x:v>5964</x:v>
       </x:c>
       <x:c r="X18" s="0">
-        <x:v>3622</x:v>
+        <x:v>5361</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:24">
@@ -1693,28 +1693,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>2.78</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>37.67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K19" s="0">
-        <x:v>3.16</x:v>
+        <x:v>3.74</x:v>
       </x:c>
       <x:c r="L19" s="0">
-        <x:v>43.61</x:v>
+        <x:v>40.57</x:v>
       </x:c>
       <x:c r="M19" s="0">
-        <x:v>4525</x:v>
+        <x:v>6867</x:v>
       </x:c>
       <x:c r="N19" s="0">
-        <x:v>4527</x:v>
+        <x:v>6871</x:v>
       </x:c>
       <x:c r="O19" s="0">
-        <x:v>4525</x:v>
+        <x:v>6869</x:v>
       </x:c>
       <x:c r="P19" s="0">
         <x:v>78</x:v>
@@ -1723,25 +1723,25 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="R19" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S19" s="0">
         <x:v>825</x:v>
       </x:c>
       <x:c r="T19" s="0">
-        <x:v>826</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="U19" s="0">
-        <x:v>826</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="V19" s="0">
-        <x:v>3621</x:v>
+        <x:v>5962</x:v>
       </x:c>
       <x:c r="W19" s="0">
-        <x:v>3622</x:v>
+        <x:v>5965</x:v>
       </x:c>
       <x:c r="X19" s="0">
-        <x:v>3621</x:v>
+        <x:v>5964</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:24">
@@ -1758,40 +1758,40 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>2.68</x:v>
+        <x:v>2.86</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>34.05</x:v>
+        <x:v>32.31</x:v>
       </x:c>
       <x:c r="K20" s="0">
-        <x:v>8.05</x:v>
+        <x:v>7.53</x:v>
       </x:c>
       <x:c r="L20" s="0">
-        <x:v>44.78</x:v>
+        <x:v>42.71</x:v>
       </x:c>
       <x:c r="M20" s="0">
-        <x:v>4528</x:v>
+        <x:v>6869</x:v>
       </x:c>
       <x:c r="N20" s="0">
-        <x:v>4531</x:v>
+        <x:v>6872</x:v>
       </x:c>
       <x:c r="O20" s="0">
-        <x:v>4530</x:v>
+        <x:v>6870</x:v>
       </x:c>
       <x:c r="P20" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="R20" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="S20" s="0">
-        <x:v>827</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="T20" s="0">
         <x:v>829</x:v>
@@ -1800,13 +1800,13 @@
         <x:v>829</x:v>
       </x:c>
       <x:c r="V20" s="0">
-        <x:v>3622</x:v>
+        <x:v>5963</x:v>
       </x:c>
       <x:c r="W20" s="0">
-        <x:v>3624</x:v>
+        <x:v>5965</x:v>
       </x:c>
       <x:c r="X20" s="0">
-        <x:v>3623</x:v>
+        <x:v>5963</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:24">
@@ -1823,55 +1823,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>21</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G21" s="0">
         <x:v>2.67</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>31.82</x:v>
+        <x:v>30.73</x:v>
       </x:c>
       <x:c r="K21" s="0">
-        <x:v>2.14</x:v>
+        <x:v>3.76</x:v>
       </x:c>
       <x:c r="L21" s="0">
-        <x:v>36.63</x:v>
+        <x:v>37.17</x:v>
       </x:c>
       <x:c r="M21" s="0">
-        <x:v>4528</x:v>
+        <x:v>6873</x:v>
       </x:c>
       <x:c r="N21" s="0">
-        <x:v>4536</x:v>
+        <x:v>8582</x:v>
       </x:c>
       <x:c r="O21" s="0">
-        <x:v>4533</x:v>
+        <x:v>7777</x:v>
       </x:c>
       <x:c r="P21" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R21" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="S21" s="0">
-        <x:v>829</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="T21" s="0">
-        <x:v>830</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="U21" s="0">
-        <x:v>830</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="V21" s="0">
-        <x:v>3619</x:v>
+        <x:v>5965</x:v>
       </x:c>
       <x:c r="W21" s="0">
-        <x:v>3626</x:v>
+        <x:v>7672</x:v>
       </x:c>
       <x:c r="X21" s="0">
-        <x:v>3624</x:v>
+        <x:v>6867</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:24">
@@ -1888,31 +1888,31 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>5</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>2.69</x:v>
+        <x:v>2.74</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>33.19</x:v>
+        <x:v>32.13</x:v>
       </x:c>
       <x:c r="K22" s="0">
-        <x:v>0.54</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="L22" s="0">
-        <x:v>36.42</x:v>
+        <x:v>37.69</x:v>
       </x:c>
       <x:c r="M22" s="0">
-        <x:v>4533</x:v>
+        <x:v>8183</x:v>
       </x:c>
       <x:c r="N22" s="0">
-        <x:v>4536</x:v>
+        <x:v>8189</x:v>
       </x:c>
       <x:c r="O22" s="0">
-        <x:v>4534</x:v>
+        <x:v>8186</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>80</x:v>
@@ -1930,13 +1930,13 @@
         <x:v>834</x:v>
       </x:c>
       <x:c r="V22" s="0">
-        <x:v>3621</x:v>
+        <x:v>7271</x:v>
       </x:c>
       <x:c r="W22" s="0">
-        <x:v>3623</x:v>
+        <x:v>7276</x:v>
       </x:c>
       <x:c r="X22" s="0">
-        <x:v>3622</x:v>
+        <x:v>7274</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:24">
@@ -1953,40 +1953,40 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>211</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2.82</x:v>
+        <x:v>2.71</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>35.94</x:v>
+        <x:v>33.67</x:v>
       </x:c>
       <x:c r="K23" s="0">
-        <x:v>21.41</x:v>
+        <x:v>7.68</x:v>
       </x:c>
       <x:c r="L23" s="0">
-        <x:v>60.17</x:v>
+        <x:v>44.06</x:v>
       </x:c>
       <x:c r="M23" s="0">
-        <x:v>4536</x:v>
+        <x:v>8184</x:v>
       </x:c>
       <x:c r="N23" s="0">
-        <x:v>4539</x:v>
+        <x:v>8188</x:v>
       </x:c>
       <x:c r="O23" s="0">
-        <x:v>4538</x:v>
+        <x:v>8186</x:v>
       </x:c>
       <x:c r="P23" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="Q23" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R23" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S23" s="0">
-        <x:v>834</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="T23" s="0">
         <x:v>836</x:v>
@@ -1995,13 +1995,13 @@
         <x:v>836</x:v>
       </x:c>
       <x:c r="V23" s="0">
-        <x:v>3623</x:v>
+        <x:v>7271</x:v>
       </x:c>
       <x:c r="W23" s="0">
-        <x:v>3625</x:v>
+        <x:v>7273</x:v>
       </x:c>
       <x:c r="X23" s="0">
-        <x:v>3624</x:v>
+        <x:v>7271</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:24">
@@ -2018,55 +2018,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>262</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>2.75</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>35.28</x:v>
+        <x:v>34.87</x:v>
       </x:c>
       <x:c r="K24" s="0">
-        <x:v>26.11</x:v>
+        <x:v>31.82</x:v>
       </x:c>
       <x:c r="L24" s="0">
-        <x:v>64.13</x:v>
+        <x:v>69.48</x:v>
       </x:c>
       <x:c r="M24" s="0">
-        <x:v>4537</x:v>
+        <x:v>6470</x:v>
       </x:c>
       <x:c r="N24" s="0">
-        <x:v>4542</x:v>
+        <x:v>8190</x:v>
       </x:c>
       <x:c r="O24" s="0">
-        <x:v>4540</x:v>
+        <x:v>7501</x:v>
       </x:c>
       <x:c r="P24" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="Q24" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="R24" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S24" s="0">
         <x:v>837</x:v>
       </x:c>
       <x:c r="T24" s="0">
-        <x:v>839</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="U24" s="0">
-        <x:v>839</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="V24" s="0">
-        <x:v>3620</x:v>
+        <x:v>5553</x:v>
       </x:c>
       <x:c r="W24" s="0">
-        <x:v>3625</x:v>
+        <x:v>7272</x:v>
       </x:c>
       <x:c r="X24" s="0">
-        <x:v>3623</x:v>
+        <x:v>6584</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:24">
@@ -2083,40 +2083,40 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>70</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>2.63</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>25.04</x:v>
+        <x:v>34.02</x:v>
       </x:c>
       <x:c r="K25" s="0">
-        <x:v>5.36</x:v>
+        <x:v>9.96</x:v>
       </x:c>
       <x:c r="L25" s="0">
-        <x:v>33.04</x:v>
+        <x:v>46.71</x:v>
       </x:c>
       <x:c r="M25" s="0">
-        <x:v>4540</x:v>
+        <x:v>6304</x:v>
       </x:c>
       <x:c r="N25" s="0">
-        <x:v>4544</x:v>
+        <x:v>6458</x:v>
       </x:c>
       <x:c r="O25" s="0">
-        <x:v>4541</x:v>
+        <x:v>6315</x:v>
       </x:c>
       <x:c r="P25" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="Q25" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="R25" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S25" s="0">
-        <x:v>840</x:v>
+        <x:v>839</x:v>
       </x:c>
       <x:c r="T25" s="0">
         <x:v>841</x:v>
@@ -2125,13 +2125,13 @@
         <x:v>841</x:v>
       </x:c>
       <x:c r="V25" s="0">
-        <x:v>3622</x:v>
+        <x:v>5384</x:v>
       </x:c>
       <x:c r="W25" s="0">
-        <x:v>3624</x:v>
+        <x:v>5540</x:v>
       </x:c>
       <x:c r="X25" s="0">
-        <x:v>3622</x:v>
+        <x:v>5396</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:24">
@@ -2148,37 +2148,37 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>54</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>2.65</x:v>
+        <x:v>2.73</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>23.85</x:v>
+        <x:v>33.03</x:v>
       </x:c>
       <x:c r="K26" s="0">
-        <x:v>4.14</x:v>
+        <x:v>8.28</x:v>
       </x:c>
       <x:c r="L26" s="0">
-        <x:v>30.65</x:v>
+        <x:v>44.04</x:v>
       </x:c>
       <x:c r="M26" s="0">
-        <x:v>4545</x:v>
+        <x:v>6307</x:v>
       </x:c>
       <x:c r="N26" s="0">
-        <x:v>4547</x:v>
+        <x:v>6309</x:v>
       </x:c>
       <x:c r="O26" s="0">
-        <x:v>4546</x:v>
+        <x:v>6308</x:v>
       </x:c>
       <x:c r="P26" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="Q26" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="R26" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S26" s="0">
         <x:v>842</x:v>
@@ -2190,13 +2190,13 @@
         <x:v>843</x:v>
       </x:c>
       <x:c r="V26" s="0">
-        <x:v>3624</x:v>
+        <x:v>5385</x:v>
       </x:c>
       <x:c r="W26" s="0">
-        <x:v>3625</x:v>
+        <x:v>5387</x:v>
       </x:c>
       <x:c r="X26" s="0">
-        <x:v>3624</x:v>
+        <x:v>5386</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:24">
@@ -2213,55 +2213,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>2.71</x:v>
+        <x:v>2.82</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>24.91</x:v>
+        <x:v>33.7</x:v>
       </x:c>
       <x:c r="K27" s="0">
-        <x:v>3.28</x:v>
+        <x:v>1.89</x:v>
       </x:c>
       <x:c r="L27" s="0">
-        <x:v>30.89</x:v>
+        <x:v>38.41</x:v>
       </x:c>
       <x:c r="M27" s="0">
-        <x:v>4545</x:v>
+        <x:v>6309</x:v>
       </x:c>
       <x:c r="N27" s="0">
-        <x:v>4552</x:v>
+        <x:v>6311</x:v>
       </x:c>
       <x:c r="O27" s="0">
-        <x:v>4549</x:v>
+        <x:v>6310</x:v>
       </x:c>
       <x:c r="P27" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="Q27" s="0">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="R27" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S27" s="0">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="T27" s="0">
         <x:v>845</x:v>
       </x:c>
-      <x:c r="T27" s="0">
-        <x:v>846</x:v>
-      </x:c>
       <x:c r="U27" s="0">
-        <x:v>846</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="V27" s="0">
-        <x:v>3621</x:v>
+        <x:v>5386</x:v>
       </x:c>
       <x:c r="W27" s="0">
-        <x:v>3627</x:v>
+        <x:v>5387</x:v>
       </x:c>
       <x:c r="X27" s="0">
-        <x:v>3625</x:v>
+        <x:v>5386</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:24">
@@ -2278,40 +2278,40 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>110</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>2.67</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>29.24</x:v>
+        <x:v>33.19</x:v>
       </x:c>
       <x:c r="K28" s="0">
-        <x:v>11.12</x:v>
+        <x:v>8.59</x:v>
       </x:c>
       <x:c r="L28" s="0">
-        <x:v>43.03</x:v>
+        <x:v>44.55</x:v>
       </x:c>
       <x:c r="M28" s="0">
-        <x:v>4547</x:v>
+        <x:v>6312</x:v>
       </x:c>
       <x:c r="N28" s="0">
-        <x:v>4550</x:v>
+        <x:v>8282</x:v>
       </x:c>
       <x:c r="O28" s="0">
-        <x:v>4549</x:v>
+        <x:v>7470</x:v>
       </x:c>
       <x:c r="P28" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="Q28" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="R28" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S28" s="0">
-        <x:v>846</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="T28" s="0">
         <x:v>848</x:v>
@@ -2320,13 +2320,13 @@
         <x:v>848</x:v>
       </x:c>
       <x:c r="V28" s="0">
-        <x:v>3622</x:v>
+        <x:v>5388</x:v>
       </x:c>
       <x:c r="W28" s="0">
-        <x:v>3624</x:v>
+        <x:v>7354</x:v>
       </x:c>
       <x:c r="X28" s="0">
-        <x:v>3623</x:v>
+        <x:v>6544</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:24">
@@ -2343,40 +2343,40 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>239</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>2.73</x:v>
+        <x:v>2.76</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>30.42</x:v>
+        <x:v>28.79</x:v>
       </x:c>
       <x:c r="K29" s="0">
-        <x:v>24.31</x:v>
+        <x:v>31.63</x:v>
       </x:c>
       <x:c r="L29" s="0">
-        <x:v>57.46</x:v>
+        <x:v>63.17</x:v>
       </x:c>
       <x:c r="M29" s="0">
-        <x:v>4551</x:v>
+        <x:v>8278</x:v>
       </x:c>
       <x:c r="N29" s="0">
-        <x:v>4555</x:v>
+        <x:v>8282</x:v>
       </x:c>
       <x:c r="O29" s="0">
-        <x:v>4553</x:v>
+        <x:v>8280</x:v>
       </x:c>
       <x:c r="P29" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="Q29" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="R29" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S29" s="0">
-        <x:v>849</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="T29" s="0">
         <x:v>850</x:v>
@@ -2385,13 +2385,13 @@
         <x:v>850</x:v>
       </x:c>
       <x:c r="V29" s="0">
-        <x:v>3624</x:v>
+        <x:v>7351</x:v>
       </x:c>
       <x:c r="W29" s="0">
-        <x:v>3626</x:v>
+        <x:v>7353</x:v>
       </x:c>
       <x:c r="X29" s="0">
-        <x:v>3625</x:v>
+        <x:v>7352</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:24">
@@ -2408,34 +2408,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>29</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>2.76</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>33.63</x:v>
+        <x:v>27.91</x:v>
       </x:c>
       <x:c r="K30" s="0">
-        <x:v>2.76</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="L30" s="0">
-        <x:v>39.16</x:v>
+        <x:v>31.06</x:v>
       </x:c>
       <x:c r="M30" s="0">
-        <x:v>4552</x:v>
+        <x:v>8256</x:v>
       </x:c>
       <x:c r="N30" s="0">
-        <x:v>4563</x:v>
+        <x:v>8289</x:v>
       </x:c>
       <x:c r="O30" s="0">
-        <x:v>4558</x:v>
+        <x:v>8285</x:v>
       </x:c>
       <x:c r="P30" s="0">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="Q30" s="0">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R30" s="0">
         <x:v>79</x:v>
@@ -2444,19 +2444,19 @@
         <x:v>851</x:v>
       </x:c>
       <x:c r="T30" s="0">
-        <x:v>852</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="U30" s="0">
-        <x:v>852</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="V30" s="0">
-        <x:v>3622</x:v>
+        <x:v>7324</x:v>
       </x:c>
       <x:c r="W30" s="0">
-        <x:v>3629</x:v>
+        <x:v>7355</x:v>
       </x:c>
       <x:c r="X30" s="0">
-        <x:v>3626</x:v>
+        <x:v>7353</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:24">
@@ -2473,28 +2473,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>124</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>2.65</x:v>
+        <x:v>2.69</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>35.18</x:v>
+        <x:v>33.51</x:v>
       </x:c>
       <x:c r="K31" s="0">
-        <x:v>12.28</x:v>
+        <x:v>9.53</x:v>
       </x:c>
       <x:c r="L31" s="0">
-        <x:v>50.11</x:v>
+        <x:v>45.73</x:v>
       </x:c>
       <x:c r="M31" s="0">
-        <x:v>4556</x:v>
+        <x:v>6798</x:v>
       </x:c>
       <x:c r="N31" s="0">
-        <x:v>4561</x:v>
+        <x:v>8240</x:v>
       </x:c>
       <x:c r="O31" s="0">
-        <x:v>4557</x:v>
+        <x:v>7525</x:v>
       </x:c>
       <x:c r="P31" s="0">
         <x:v>79</x:v>
@@ -2503,25 +2503,25 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="R31" s="0">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S31" s="0">
-        <x:v>853</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="T31" s="0">
-        <x:v>855</x:v>
+        <x:v>856</x:v>
       </x:c>
       <x:c r="U31" s="0">
-        <x:v>855</x:v>
+        <x:v>856</x:v>
       </x:c>
       <x:c r="V31" s="0">
-        <x:v>3622</x:v>
+        <x:v>5864</x:v>
       </x:c>
       <x:c r="W31" s="0">
-        <x:v>3625</x:v>
+        <x:v>7305</x:v>
       </x:c>
       <x:c r="X31" s="0">
-        <x:v>3623</x:v>
+        <x:v>6590</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:24">
@@ -2538,31 +2538,31 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>346</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>2.68</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>38.66</x:v>
+        <x:v>36.14</x:v>
       </x:c>
       <x:c r="K32" s="0">
-        <x:v>35.01</x:v>
+        <x:v>28.96</x:v>
       </x:c>
       <x:c r="L32" s="0">
-        <x:v>76.35</x:v>
+        <x:v>67.9</x:v>
       </x:c>
       <x:c r="M32" s="0">
-        <x:v>4560</x:v>
+        <x:v>6792</x:v>
       </x:c>
       <x:c r="N32" s="0">
-        <x:v>4566</x:v>
+        <x:v>6799</x:v>
       </x:c>
       <x:c r="O32" s="0">
-        <x:v>4563</x:v>
+        <x:v>6796</x:v>
       </x:c>
       <x:c r="P32" s="0">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q32" s="0">
         <x:v>82</x:v>
@@ -2571,22 +2571,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="S32" s="0">
-        <x:v>856</x:v>
+        <x:v>857</x:v>
       </x:c>
       <x:c r="T32" s="0">
-        <x:v>857</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="U32" s="0">
-        <x:v>857</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="V32" s="0">
-        <x:v>3624</x:v>
+        <x:v>5856</x:v>
       </x:c>
       <x:c r="W32" s="0">
-        <x:v>3627</x:v>
+        <x:v>5858</x:v>
       </x:c>
       <x:c r="X32" s="0">
-        <x:v>3626</x:v>
+        <x:v>5857</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:24">
@@ -2603,28 +2603,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>67</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>2.68</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>36.06</x:v>
+        <x:v>29.89</x:v>
       </x:c>
       <x:c r="K33" s="0">
-        <x:v>6.73</x:v>
+        <x:v>7.67</x:v>
       </x:c>
       <x:c r="L33" s="0">
-        <x:v>45.47</x:v>
+        <x:v>40.16</x:v>
       </x:c>
       <x:c r="M33" s="0">
-        <x:v>4563</x:v>
+        <x:v>6796</x:v>
       </x:c>
       <x:c r="N33" s="0">
-        <x:v>4565</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="O33" s="0">
-        <x:v>4564</x:v>
+        <x:v>6798</x:v>
       </x:c>
       <x:c r="P33" s="0">
         <x:v>80</x:v>
@@ -2636,22 +2636,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="S33" s="0">
-        <x:v>858</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="T33" s="0">
-        <x:v>859</x:v>
+        <x:v>860</x:v>
       </x:c>
       <x:c r="U33" s="0">
-        <x:v>859</x:v>
+        <x:v>860</x:v>
       </x:c>
       <x:c r="V33" s="0">
-        <x:v>3624</x:v>
+        <x:v>5855</x:v>
       </x:c>
       <x:c r="W33" s="0">
-        <x:v>3626</x:v>
+        <x:v>5859</x:v>
       </x:c>
       <x:c r="X33" s="0">
-        <x:v>3624</x:v>
+        <x:v>5857</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:24">
@@ -2668,28 +2668,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>2.79</x:v>
+        <x:v>2.76</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>37.24</x:v>
+        <x:v>33.9</x:v>
       </x:c>
       <x:c r="K34" s="0">
-        <x:v>4.67</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="L34" s="0">
-        <x:v>44.7</x:v>
+        <x:v>40.18</x:v>
       </x:c>
       <x:c r="M34" s="0">
-        <x:v>4567</x:v>
+        <x:v>6579</x:v>
       </x:c>
       <x:c r="N34" s="0">
-        <x:v>4568</x:v>
+        <x:v>6785</x:v>
       </x:c>
       <x:c r="O34" s="0">
-        <x:v>4567</x:v>
+        <x:v>6599</x:v>
       </x:c>
       <x:c r="P34" s="0">
         <x:v>80</x:v>
@@ -2704,19 +2704,19 @@
         <x:v>861</x:v>
       </x:c>
       <x:c r="T34" s="0">
-        <x:v>862</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="U34" s="0">
-        <x:v>862</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="V34" s="0">
-        <x:v>3625</x:v>
+        <x:v>5636</x:v>
       </x:c>
       <x:c r="W34" s="0">
-        <x:v>3627</x:v>
+        <x:v>5843</x:v>
       </x:c>
       <x:c r="X34" s="0">
-        <x:v>3625</x:v>
+        <x:v>5655</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:24">
@@ -2733,28 +2733,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>50</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>2.79</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>38.34</x:v>
+        <x:v>33.96</x:v>
       </x:c>
       <x:c r="K35" s="0">
-        <x:v>5</x:v>
+        <x:v>6.26</x:v>
       </x:c>
       <x:c r="L35" s="0">
-        <x:v>46.13</x:v>
+        <x:v>43.02</x:v>
       </x:c>
       <x:c r="M35" s="0">
-        <x:v>4567</x:v>
+        <x:v>6582</x:v>
       </x:c>
       <x:c r="N35" s="0">
-        <x:v>4572</x:v>
+        <x:v>6585</x:v>
       </x:c>
       <x:c r="O35" s="0">
-        <x:v>4570</x:v>
+        <x:v>6583</x:v>
       </x:c>
       <x:c r="P35" s="0">
         <x:v>80</x:v>
@@ -2766,22 +2766,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="S35" s="0">
-        <x:v>863</x:v>
+        <x:v>864</x:v>
       </x:c>
       <x:c r="T35" s="0">
-        <x:v>865</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="U35" s="0">
         <x:v>865</x:v>
       </x:c>
       <x:c r="V35" s="0">
-        <x:v>3622</x:v>
+        <x:v>5637</x:v>
       </x:c>
       <x:c r="W35" s="0">
-        <x:v>3627</x:v>
+        <x:v>5639</x:v>
       </x:c>
       <x:c r="X35" s="0">
-        <x:v>3626</x:v>
+        <x:v>5638</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:24">
@@ -2798,28 +2798,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>55</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.77</x:v>
+        <x:v>2.66</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>28.6</x:v>
+        <x:v>31.91</x:v>
       </x:c>
       <x:c r="K36" s="0">
-        <x:v>4.48</x:v>
+        <x:v>8.27</x:v>
       </x:c>
       <x:c r="L36" s="0">
-        <x:v>35.85</x:v>
+        <x:v>42.84</x:v>
       </x:c>
       <x:c r="M36" s="0">
-        <x:v>4554</x:v>
+        <x:v>6584</x:v>
       </x:c>
       <x:c r="N36" s="0">
-        <x:v>4571</x:v>
+        <x:v>6587</x:v>
       </x:c>
       <x:c r="O36" s="0">
-        <x:v>4562</x:v>
+        <x:v>6586</x:v>
       </x:c>
       <x:c r="P36" s="0">
         <x:v>80</x:v>
@@ -2831,22 +2831,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="S36" s="0">
-        <x:v>851</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="T36" s="0">
         <x:v>867</x:v>
       </x:c>
       <x:c r="U36" s="0">
-        <x:v>858</x:v>
+        <x:v>867</x:v>
       </x:c>
       <x:c r="V36" s="0">
-        <x:v>3624</x:v>
+        <x:v>5636</x:v>
       </x:c>
       <x:c r="W36" s="0">
-        <x:v>3625</x:v>
+        <x:v>5639</x:v>
       </x:c>
       <x:c r="X36" s="0">
-        <x:v>3624</x:v>
+        <x:v>5639</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:24">
@@ -2863,28 +2863,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>2.75</x:v>
+        <x:v>2.71</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>22.63</x:v>
+        <x:v>30.93</x:v>
       </x:c>
       <x:c r="K37" s="0">
-        <x:v>1.62</x:v>
+        <x:v>4.16</x:v>
       </x:c>
       <x:c r="L37" s="0">
-        <x:v>27</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="M37" s="0">
-        <x:v>4557</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="N37" s="0">
-        <x:v>4560</x:v>
+        <x:v>6586</x:v>
       </x:c>
       <x:c r="O37" s="0">
-        <x:v>4559</x:v>
+        <x:v>6122</x:v>
       </x:c>
       <x:c r="P37" s="0">
         <x:v>80</x:v>
@@ -2896,22 +2896,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="S37" s="0">
-        <x:v>852</x:v>
+        <x:v>868</x:v>
       </x:c>
       <x:c r="T37" s="0">
-        <x:v>854</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="U37" s="0">
-        <x:v>854</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="V37" s="0">
-        <x:v>3625</x:v>
+        <x:v>4650</x:v>
       </x:c>
       <x:c r="W37" s="0">
-        <x:v>3627</x:v>
+        <x:v>5636</x:v>
       </x:c>
       <x:c r="X37" s="0">
-        <x:v>3625</x:v>
+        <x:v>5172</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:24">
@@ -2928,28 +2928,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>34</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>2.92</x:v>
+        <x:v>2.74</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>24.13</x:v>
+        <x:v>33.59</x:v>
       </x:c>
       <x:c r="K38" s="0">
-        <x:v>2.63</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="L38" s="0">
-        <x:v>29.69</x:v>
+        <x:v>36.77</x:v>
       </x:c>
       <x:c r="M38" s="0">
         <x:v>4561</x:v>
       </x:c>
       <x:c r="N38" s="0">
-        <x:v>4564</x:v>
+        <x:v>5587</x:v>
       </x:c>
       <x:c r="O38" s="0">
-        <x:v>4562</x:v>
+        <x:v>5074</x:v>
       </x:c>
       <x:c r="P38" s="0">
         <x:v>80</x:v>
@@ -2961,22 +2961,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="S38" s="0">
-        <x:v>855</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="T38" s="0">
-        <x:v>856</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="U38" s="0">
-        <x:v>856</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="V38" s="0">
-        <x:v>3627</x:v>
+        <x:v>3608</x:v>
       </x:c>
       <x:c r="W38" s="0">
-        <x:v>3629</x:v>
+        <x:v>4636</x:v>
       </x:c>
       <x:c r="X38" s="0">
-        <x:v>3627</x:v>
+        <x:v>4121</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:24">
@@ -2996,25 +2996,25 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>2.7</x:v>
+        <x:v>2.75</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>29.05</x:v>
+        <x:v>33.35</x:v>
       </x:c>
       <x:c r="K39" s="0">
-        <x:v>14.94</x:v>
+        <x:v>16.31</x:v>
       </x:c>
       <x:c r="L39" s="0">
-        <x:v>46.69</x:v>
+        <x:v>52.41</x:v>
       </x:c>
       <x:c r="M39" s="0">
-        <x:v>4561</x:v>
+        <x:v>4459</x:v>
       </x:c>
       <x:c r="N39" s="0">
-        <x:v>4568</x:v>
+        <x:v>4548</x:v>
       </x:c>
       <x:c r="O39" s="0">
-        <x:v>4564</x:v>
+        <x:v>4463</x:v>
       </x:c>
       <x:c r="P39" s="0">
         <x:v>80</x:v>
@@ -3026,22 +3026,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="S39" s="0">
-        <x:v>857</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="T39" s="0">
-        <x:v>858</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="U39" s="0">
-        <x:v>858</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="V39" s="0">
-        <x:v>3623</x:v>
+        <x:v>3504</x:v>
       </x:c>
       <x:c r="W39" s="0">
-        <x:v>3629</x:v>
+        <x:v>3595</x:v>
       </x:c>
       <x:c r="X39" s="0">
-        <x:v>3627</x:v>
+        <x:v>3509</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:24">
@@ -3058,28 +3058,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>225</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2.8</x:v>
+        <x:v>2.66</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>25.77</x:v>
+        <x:v>33.14</x:v>
       </x:c>
       <x:c r="K40" s="0">
-        <x:v>20.7</x:v>
+        <x:v>23.14</x:v>
       </x:c>
       <x:c r="L40" s="0">
-        <x:v>49.27</x:v>
+        <x:v>58.95</x:v>
       </x:c>
       <x:c r="M40" s="0">
-        <x:v>4564</x:v>
+        <x:v>4460</x:v>
       </x:c>
       <x:c r="N40" s="0">
-        <x:v>4567</x:v>
+        <x:v>4462</x:v>
       </x:c>
       <x:c r="O40" s="0">
-        <x:v>4565</x:v>
+        <x:v>4461</x:v>
       </x:c>
       <x:c r="P40" s="0">
         <x:v>80</x:v>
@@ -3091,22 +3091,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="S40" s="0">
-        <x:v>859</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="T40" s="0">
-        <x:v>860</x:v>
+        <x:v>877</x:v>
       </x:c>
       <x:c r="U40" s="0">
-        <x:v>860</x:v>
+        <x:v>877</x:v>
       </x:c>
       <x:c r="V40" s="0">
-        <x:v>3624</x:v>
+        <x:v>3504</x:v>
       </x:c>
       <x:c r="W40" s="0">
-        <x:v>3626</x:v>
+        <x:v>3505</x:v>
       </x:c>
       <x:c r="X40" s="0">
-        <x:v>3625</x:v>
+        <x:v>3504</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:24">
@@ -3123,28 +3123,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>124</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>2.64</x:v>
+        <x:v>2.73</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>36.16</x:v>
+        <x:v>33.24</x:v>
       </x:c>
       <x:c r="K41" s="0">
-        <x:v>12.29</x:v>
+        <x:v>1.96</x:v>
       </x:c>
       <x:c r="L41" s="0">
-        <x:v>51.09</x:v>
+        <x:v>37.93</x:v>
       </x:c>
       <x:c r="M41" s="0">
-        <x:v>4567</x:v>
+        <x:v>4463</x:v>
       </x:c>
       <x:c r="N41" s="0">
-        <x:v>4571</x:v>
+        <x:v>4466</x:v>
       </x:c>
       <x:c r="O41" s="0">
-        <x:v>4569</x:v>
+        <x:v>4465</x:v>
       </x:c>
       <x:c r="P41" s="0">
         <x:v>80</x:v>
@@ -3156,22 +3156,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="S41" s="0">
-        <x:v>862</x:v>
+        <x:v>878</x:v>
       </x:c>
       <x:c r="T41" s="0">
-        <x:v>863</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="U41" s="0">
-        <x:v>863</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="V41" s="0">
-        <x:v>3624</x:v>
+        <x:v>3505</x:v>
       </x:c>
       <x:c r="W41" s="0">
-        <x:v>3628</x:v>
+        <x:v>3507</x:v>
       </x:c>
       <x:c r="X41" s="0">
-        <x:v>3626</x:v>
+        <x:v>3506</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:24">
@@ -3188,55 +3188,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>78</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>2.73</x:v>
+        <x:v>2.59</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>35.33</x:v>
+        <x:v>32.37</x:v>
       </x:c>
       <x:c r="K42" s="0">
-        <x:v>7.8</x:v>
+        <x:v>10.13</x:v>
       </x:c>
       <x:c r="L42" s="0">
-        <x:v>45.85</x:v>
+        <x:v>45.09</x:v>
       </x:c>
       <x:c r="M42" s="0">
-        <x:v>4569</x:v>
+        <x:v>4463</x:v>
       </x:c>
       <x:c r="N42" s="0">
-        <x:v>4572</x:v>
+        <x:v>4468</x:v>
       </x:c>
       <x:c r="O42" s="0">
-        <x:v>4570</x:v>
+        <x:v>4467</x:v>
       </x:c>
       <x:c r="P42" s="0">
         <x:v>80</x:v>
       </x:c>
       <x:c r="Q42" s="0">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R42" s="0">
         <x:v>80</x:v>
       </x:c>
       <x:c r="S42" s="0">
-        <x:v>864</x:v>
+        <x:v>880</x:v>
       </x:c>
       <x:c r="T42" s="0">
-        <x:v>865</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="U42" s="0">
-        <x:v>865</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="V42" s="0">
-        <x:v>3624</x:v>
+        <x:v>3502</x:v>
       </x:c>
       <x:c r="W42" s="0">
-        <x:v>3626</x:v>
+        <x:v>3507</x:v>
       </x:c>
       <x:c r="X42" s="0">
-        <x:v>3625</x:v>
+        <x:v>3506</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:24">
@@ -3253,55 +3253,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>99</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>2.8</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>39.44</x:v>
+        <x:v>32.73</x:v>
       </x:c>
       <x:c r="K43" s="0">
-        <x:v>10.05</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="L43" s="0">
-        <x:v>52.3</x:v>
+        <x:v>46.36</x:v>
       </x:c>
       <x:c r="M43" s="0">
-        <x:v>3717</x:v>
+        <x:v>4466</x:v>
       </x:c>
       <x:c r="N43" s="0">
-        <x:v>4574</x:v>
+        <x:v>4470</x:v>
       </x:c>
       <x:c r="O43" s="0">
-        <x:v>4202</x:v>
+        <x:v>4468</x:v>
       </x:c>
       <x:c r="P43" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q43" s="0">
         <x:v>80</x:v>
       </x:c>
       <x:c r="R43" s="0">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S43" s="0">
-        <x:v>700</x:v>
+        <x:v>882</x:v>
       </x:c>
       <x:c r="T43" s="0">
-        <x:v>868</x:v>
+        <x:v>884</x:v>
       </x:c>
       <x:c r="U43" s="0">
-        <x:v>794</x:v>
+        <x:v>884</x:v>
       </x:c>
       <x:c r="V43" s="0">
-        <x:v>2939</x:v>
+        <x:v>3504</x:v>
       </x:c>
       <x:c r="W43" s="0">
-        <x:v>3626</x:v>
+        <x:v>3506</x:v>
       </x:c>
       <x:c r="X43" s="0">
-        <x:v>3329</x:v>
+        <x:v>3504</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:24">
@@ -3318,55 +3318,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>269</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>2.78</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>38.69</x:v>
+        <x:v>32.87</x:v>
       </x:c>
       <x:c r="K44" s="0">
-        <x:v>27.27</x:v>
+        <x:v>17.94</x:v>
       </x:c>
       <x:c r="L44" s="0">
-        <x:v>68.73</x:v>
+        <x:v>53.66</x:v>
       </x:c>
       <x:c r="M44" s="0">
-        <x:v>3716</x:v>
+        <x:v>4471</x:v>
       </x:c>
       <x:c r="N44" s="0">
-        <x:v>3721</x:v>
+        <x:v>4473</x:v>
       </x:c>
       <x:c r="O44" s="0">
-        <x:v>3719</x:v>
+        <x:v>4472</x:v>
       </x:c>
       <x:c r="P44" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q44" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R44" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S44" s="0">
-        <x:v>701</x:v>
+        <x:v>885</x:v>
       </x:c>
       <x:c r="T44" s="0">
-        <x:v>702</x:v>
+        <x:v>886</x:v>
       </x:c>
       <x:c r="U44" s="0">
-        <x:v>702</x:v>
+        <x:v>886</x:v>
       </x:c>
       <x:c r="V44" s="0">
-        <x:v>2937</x:v>
+        <x:v>3506</x:v>
       </x:c>
       <x:c r="W44" s="0">
-        <x:v>2941</x:v>
+        <x:v>3507</x:v>
       </x:c>
       <x:c r="X44" s="0">
-        <x:v>2939</x:v>
+        <x:v>3506</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:24">
@@ -3383,55 +3383,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>230</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.71</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>30.64</x:v>
+        <x:v>27.69</x:v>
       </x:c>
       <x:c r="K45" s="0">
-        <x:v>23.01</x:v>
+        <x:v>11.67</x:v>
       </x:c>
       <x:c r="L45" s="0">
-        <x:v>56.36</x:v>
+        <x:v>42.09</x:v>
       </x:c>
       <x:c r="M45" s="0">
-        <x:v>3720</x:v>
+        <x:v>4472</x:v>
       </x:c>
       <x:c r="N45" s="0">
-        <x:v>3723</x:v>
+        <x:v>4478</x:v>
       </x:c>
       <x:c r="O45" s="0">
-        <x:v>3722</x:v>
+        <x:v>4476</x:v>
       </x:c>
       <x:c r="P45" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q45" s="0">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R45" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S45" s="0">
-        <x:v>703</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="T45" s="0">
-        <x:v>705</x:v>
+        <x:v>890</x:v>
       </x:c>
       <x:c r="U45" s="0">
-        <x:v>705</x:v>
+        <x:v>890</x:v>
       </x:c>
       <x:c r="V45" s="0">
-        <x:v>2938</x:v>
+        <x:v>3502</x:v>
       </x:c>
       <x:c r="W45" s="0">
-        <x:v>2940</x:v>
+        <x:v>3507</x:v>
       </x:c>
       <x:c r="X45" s="0">
-        <x:v>2939</x:v>
+        <x:v>3506</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:24">
@@ -3451,52 +3451,52 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.73</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>31.37</x:v>
+        <x:v>27.53</x:v>
       </x:c>
       <x:c r="K46" s="0">
-        <x:v>2.57</x:v>
+        <x:v>2.21</x:v>
       </x:c>
       <x:c r="L46" s="0">
-        <x:v>36.66</x:v>
+        <x:v>32.47</x:v>
       </x:c>
       <x:c r="M46" s="0">
-        <x:v>3722</x:v>
+        <x:v>4475</x:v>
       </x:c>
       <x:c r="N46" s="0">
-        <x:v>3725</x:v>
+        <x:v>4478</x:v>
       </x:c>
       <x:c r="O46" s="0">
-        <x:v>3725</x:v>
+        <x:v>4476</x:v>
       </x:c>
       <x:c r="P46" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q46" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R46" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S46" s="0">
-        <x:v>706</x:v>
+        <x:v>891</x:v>
       </x:c>
       <x:c r="T46" s="0">
-        <x:v>707</x:v>
+        <x:v>892</x:v>
       </x:c>
       <x:c r="U46" s="0">
-        <x:v>707</x:v>
+        <x:v>892</x:v>
       </x:c>
       <x:c r="V46" s="0">
-        <x:v>2937</x:v>
+        <x:v>3504</x:v>
       </x:c>
       <x:c r="W46" s="0">
-        <x:v>2940</x:v>
+        <x:v>3505</x:v>
       </x:c>
       <x:c r="X46" s="0">
-        <x:v>2940</x:v>
+        <x:v>3504</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:24">
@@ -3513,55 +3513,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>281</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>2.78</x:v>
+        <x:v>2.84</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>38.8</x:v>
+        <x:v>32.09</x:v>
       </x:c>
       <x:c r="K47" s="0">
-        <x:v>30.48</x:v>
+        <x:v>27.34</x:v>
       </x:c>
       <x:c r="L47" s="0">
-        <x:v>72.06</x:v>
+        <x:v>62.27</x:v>
       </x:c>
       <x:c r="M47" s="0">
-        <x:v>3725</x:v>
+        <x:v>4479</x:v>
       </x:c>
       <x:c r="N47" s="0">
-        <x:v>3729</x:v>
+        <x:v>4483</x:v>
       </x:c>
       <x:c r="O47" s="0">
-        <x:v>3727</x:v>
+        <x:v>4482</x:v>
       </x:c>
       <x:c r="P47" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q47" s="0">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R47" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S47" s="0">
-        <x:v>708</x:v>
+        <x:v>893</x:v>
       </x:c>
       <x:c r="T47" s="0">
-        <x:v>710</x:v>
+        <x:v>895</x:v>
       </x:c>
       <x:c r="U47" s="0">
-        <x:v>710</x:v>
+        <x:v>895</x:v>
       </x:c>
       <x:c r="V47" s="0">
-        <x:v>2938</x:v>
+        <x:v>3506</x:v>
       </x:c>
       <x:c r="W47" s="0">
-        <x:v>2941</x:v>
+        <x:v>3508</x:v>
       </x:c>
       <x:c r="X47" s="0">
-        <x:v>2939</x:v>
+        <x:v>3507</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:24">
@@ -3578,55 +3578,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>333</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>2.64</x:v>
+        <x:v>2.82</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>42.16</x:v>
+        <x:v>35.25</x:v>
       </x:c>
       <x:c r="K48" s="0">
-        <x:v>35.52</x:v>
+        <x:v>19.55</x:v>
       </x:c>
       <x:c r="L48" s="0">
-        <x:v>80.32</x:v>
+        <x:v>57.62</x:v>
       </x:c>
       <x:c r="M48" s="0">
-        <x:v>3728</x:v>
+        <x:v>4480</x:v>
       </x:c>
       <x:c r="N48" s="0">
-        <x:v>3731</x:v>
+        <x:v>4485</x:v>
       </x:c>
       <x:c r="O48" s="0">
-        <x:v>3729</x:v>
+        <x:v>4483</x:v>
       </x:c>
       <x:c r="P48" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q48" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R48" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S48" s="0">
-        <x:v>711</x:v>
+        <x:v>896</x:v>
       </x:c>
       <x:c r="T48" s="0">
-        <x:v>712</x:v>
+        <x:v>897</x:v>
       </x:c>
       <x:c r="U48" s="0">
-        <x:v>712</x:v>
+        <x:v>897</x:v>
       </x:c>
       <x:c r="V48" s="0">
-        <x:v>2939</x:v>
+        <x:v>3503</x:v>
       </x:c>
       <x:c r="W48" s="0">
-        <x:v>2941</x:v>
+        <x:v>3508</x:v>
       </x:c>
       <x:c r="X48" s="0">
-        <x:v>2940</x:v>
+        <x:v>3506</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:24">
@@ -3643,55 +3643,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>249</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>2.7</x:v>
+        <x:v>2.86</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>37.29</x:v>
+        <x:v>31.6</x:v>
       </x:c>
       <x:c r="K49" s="0">
-        <x:v>26.36</x:v>
+        <x:v>30.45</x:v>
       </x:c>
       <x:c r="L49" s="0">
-        <x:v>66.36</x:v>
+        <x:v>64.91</x:v>
       </x:c>
       <x:c r="M49" s="0">
-        <x:v>3730</x:v>
+        <x:v>4483</x:v>
       </x:c>
       <x:c r="N49" s="0">
-        <x:v>3735</x:v>
+        <x:v>4486</x:v>
       </x:c>
       <x:c r="O49" s="0">
-        <x:v>3732</x:v>
+        <x:v>4486</x:v>
       </x:c>
       <x:c r="P49" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Q49" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R49" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S49" s="0">
-        <x:v>714</x:v>
+        <x:v>898</x:v>
       </x:c>
       <x:c r="T49" s="0">
-        <x:v>715</x:v>
+        <x:v>899</x:v>
       </x:c>
       <x:c r="U49" s="0">
-        <x:v>715</x:v>
+        <x:v>899</x:v>
       </x:c>
       <x:c r="V49" s="0">
-        <x:v>2939</x:v>
+        <x:v>3505</x:v>
       </x:c>
       <x:c r="W49" s="0">
-        <x:v>2942</x:v>
+        <x:v>3507</x:v>
       </x:c>
       <x:c r="X49" s="0">
-        <x:v>2940</x:v>
+        <x:v>3506</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:24">
@@ -3708,55 +3708,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>2.82</x:v>
+        <x:v>2.74</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>38.42</x:v>
+        <x:v>35.69</x:v>
       </x:c>
       <x:c r="K50" s="0">
-        <x:v>3.63</x:v>
+        <x:v>2.85</x:v>
       </x:c>
       <x:c r="L50" s="0">
-        <x:v>44.87</x:v>
+        <x:v>41.28</x:v>
       </x:c>
       <x:c r="M50" s="0">
-        <x:v>3727</x:v>
+        <x:v>4478</x:v>
       </x:c>
       <x:c r="N50" s="0">
-        <x:v>3740</x:v>
+        <x:v>4491</x:v>
       </x:c>
       <x:c r="O50" s="0">
-        <x:v>3734</x:v>
+        <x:v>4483</x:v>
       </x:c>
       <x:c r="P50" s="0">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="Q50" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R50" s="0">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="S50" s="0">
-        <x:v>716</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="T50" s="0">
-        <x:v>717</x:v>
+        <x:v>902</x:v>
       </x:c>
       <x:c r="U50" s="0">
-        <x:v>717</x:v>
+        <x:v>901</x:v>
       </x:c>
       <x:c r="V50" s="0">
-        <x:v>2935</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="W50" s="0">
-        <x:v>2943</x:v>
+        <x:v>3508</x:v>
       </x:c>
       <x:c r="X50" s="0">
-        <x:v>2940</x:v>
+        <x:v>3503</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:24">
@@ -3773,55 +3773,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>2.91</x:v>
+        <x:v>2.68</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>36.32</x:v>
+        <x:v>33.85</x:v>
       </x:c>
       <x:c r="K51" s="0">
-        <x:v>3.46</x:v>
+        <x:v>3.92</x:v>
       </x:c>
       <x:c r="L51" s="0">
-        <x:v>42.7</x:v>
+        <x:v>40.45</x:v>
       </x:c>
       <x:c r="M51" s="0">
-        <x:v>3730</x:v>
+        <x:v>4481</x:v>
       </x:c>
       <x:c r="N51" s="0">
-        <x:v>3739</x:v>
+        <x:v>4485</x:v>
       </x:c>
       <x:c r="O51" s="0">
-        <x:v>3733</x:v>
+        <x:v>4483</x:v>
       </x:c>
       <x:c r="P51" s="0">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="Q51" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="R51" s="0">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S51" s="0">
-        <x:v>718</x:v>
+        <x:v>902</x:v>
       </x:c>
       <x:c r="T51" s="0">
-        <x:v>719</x:v>
+        <x:v>904</x:v>
       </x:c>
       <x:c r="U51" s="0">
-        <x:v>719</x:v>
+        <x:v>903</x:v>
       </x:c>
       <x:c r="V51" s="0">
-        <x:v>2936</x:v>
+        <x:v>3502</x:v>
       </x:c>
       <x:c r="W51" s="0">
-        <x:v>2942</x:v>
+        <x:v>3504</x:v>
       </x:c>
       <x:c r="X51" s="0">
-        <x:v>2938</x:v>
+        <x:v>3503</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:24">
@@ -3838,55 +3838,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>83</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>2.61</x:v>
+        <x:v>2.76</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>34.78</x:v>
+        <x:v>32.01</x:v>
       </x:c>
       <x:c r="K52" s="0">
-        <x:v>8.59</x:v>
+        <x:v>11.51</x:v>
       </x:c>
       <x:c r="L52" s="0">
-        <x:v>45.97</x:v>
+        <x:v>46.29</x:v>
       </x:c>
       <x:c r="M52" s="0">
-        <x:v>3740</x:v>
+        <x:v>4486</x:v>
       </x:c>
       <x:c r="N52" s="0">
-        <x:v>3744</x:v>
+        <x:v>4495</x:v>
       </x:c>
       <x:c r="O52" s="0">
-        <x:v>3742</x:v>
+        <x:v>4488</x:v>
       </x:c>
       <x:c r="P52" s="0">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="Q52" s="0">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R52" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="S52" s="0">
-        <x:v>720</x:v>
+        <x:v>904</x:v>
       </x:c>
       <x:c r="T52" s="0">
-        <x:v>722</x:v>
+        <x:v>906</x:v>
       </x:c>
       <x:c r="U52" s="0">
-        <x:v>722</x:v>
+        <x:v>906</x:v>
       </x:c>
       <x:c r="V52" s="0">
-        <x:v>2942</x:v>
+        <x:v>3504</x:v>
       </x:c>
       <x:c r="W52" s="0">
-        <x:v>2944</x:v>
+        <x:v>3509</x:v>
       </x:c>
       <x:c r="X52" s="0">
-        <x:v>2942</x:v>
+        <x:v>3505</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:24">
@@ -3903,55 +3903,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>61</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>2.76</x:v>
+        <x:v>2.69</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>32.84</x:v>
+        <x:v>30.4</x:v>
       </x:c>
       <x:c r="K53" s="0">
-        <x:v>6.1</x:v>
+        <x:v>2.01</x:v>
       </x:c>
       <x:c r="L53" s="0">
-        <x:v>41.7</x:v>
+        <x:v>35.09</x:v>
       </x:c>
       <x:c r="M53" s="0">
-        <x:v>3743</x:v>
+        <x:v>4483</x:v>
       </x:c>
       <x:c r="N53" s="0">
-        <x:v>3747</x:v>
+        <x:v>4491</x:v>
       </x:c>
       <x:c r="O53" s="0">
-        <x:v>3746</x:v>
+        <x:v>4488</x:v>
       </x:c>
       <x:c r="P53" s="0">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="Q53" s="0">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="R53" s="0">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="S53" s="0">
-        <x:v>723</x:v>
+        <x:v>907</x:v>
       </x:c>
       <x:c r="T53" s="0">
-        <x:v>724</x:v>
+        <x:v>908</x:v>
       </x:c>
       <x:c r="U53" s="0">
-        <x:v>724</x:v>
+        <x:v>908</x:v>
       </x:c>
       <x:c r="V53" s="0">
-        <x:v>2940</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="W53" s="0">
-        <x:v>2945</x:v>
+        <x:v>3506</x:v>
       </x:c>
       <x:c r="X53" s="0">
-        <x:v>2944</x:v>
+        <x:v>3504</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:24">
@@ -3968,55 +3968,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>29</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>2.86</x:v>
+        <x:v>2.74</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>35.39</x:v>
+        <x:v>32.21</x:v>
       </x:c>
       <x:c r="K54" s="0">
-        <x:v>2.9</x:v>
+        <x:v>0.32</x:v>
       </x:c>
       <x:c r="L54" s="0">
-        <x:v>41.15</x:v>
+        <x:v>35.27</x:v>
       </x:c>
       <x:c r="M54" s="0">
-        <x:v>3745</x:v>
+        <x:v>4486</x:v>
       </x:c>
       <x:c r="N54" s="0">
-        <x:v>3748</x:v>
+        <x:v>4498</x:v>
       </x:c>
       <x:c r="O54" s="0">
-        <x:v>3746</x:v>
+        <x:v>4492</x:v>
       </x:c>
       <x:c r="P54" s="0">
-        <x:v>78</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="Q54" s="0">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R54" s="0">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S54" s="0">
-        <x:v>725</x:v>
+        <x:v>909</x:v>
       </x:c>
       <x:c r="T54" s="0">
-        <x:v>726</x:v>
+        <x:v>911</x:v>
       </x:c>
       <x:c r="U54" s="0">
-        <x:v>726</x:v>
+        <x:v>911</x:v>
       </x:c>
       <x:c r="V54" s="0">
-        <x:v>2941</x:v>
+        <x:v>3501</x:v>
       </x:c>
       <x:c r="W54" s="0">
-        <x:v>2943</x:v>
+        <x:v>3507</x:v>
       </x:c>
       <x:c r="X54" s="0">
-        <x:v>2942</x:v>
+        <x:v>3504</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:24">
@@ -4033,55 +4033,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>222</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>2.64</x:v>
+        <x:v>2.72</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>37.05</x:v>
+        <x:v>33.39</x:v>
       </x:c>
       <x:c r="K55" s="0">
-        <x:v>22.91</x:v>
+        <x:v>16.11</x:v>
       </x:c>
       <x:c r="L55" s="0">
-        <x:v>62.61</x:v>
+        <x:v>52.21</x:v>
       </x:c>
       <x:c r="M55" s="0">
-        <x:v>3749</x:v>
+        <x:v>4494</x:v>
       </x:c>
       <x:c r="N55" s="0">
-        <x:v>3753</x:v>
+        <x:v>4503</x:v>
       </x:c>
       <x:c r="O55" s="0">
-        <x:v>3751</x:v>
+        <x:v>4498</x:v>
       </x:c>
       <x:c r="P55" s="0">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="Q55" s="0">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R55" s="0">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S55" s="0">
-        <x:v>727</x:v>
+        <x:v>912</x:v>
       </x:c>
       <x:c r="T55" s="0">
-        <x:v>729</x:v>
+        <x:v>913</x:v>
       </x:c>
       <x:c r="U55" s="0">
-        <x:v>729</x:v>
+        <x:v>913</x:v>
       </x:c>
       <x:c r="V55" s="0">
-        <x:v>2943</x:v>
+        <x:v>3505</x:v>
       </x:c>
       <x:c r="W55" s="0">
-        <x:v>2946</x:v>
+        <x:v>3509</x:v>
       </x:c>
       <x:c r="X55" s="0">
-        <x:v>2944</x:v>
+        <x:v>3507</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:24">
@@ -4098,55 +4098,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F56" s="0">
-        <x:v>270</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="G56" s="0">
-        <x:v>2.75</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="H56" s="0">
-        <x:v>36.94</x:v>
+        <x:v>33.36</x:v>
       </x:c>
       <x:c r="K56" s="0">
-        <x:v>26.9</x:v>
+        <x:v>19.18</x:v>
       </x:c>
       <x:c r="L56" s="0">
-        <x:v>66.59</x:v>
+        <x:v>55.33</x:v>
       </x:c>
       <x:c r="M56" s="0">
-        <x:v>3750</x:v>
+        <x:v>4495</x:v>
       </x:c>
       <x:c r="N56" s="0">
-        <x:v>3756</x:v>
+        <x:v>4507</x:v>
       </x:c>
       <x:c r="O56" s="0">
-        <x:v>3753</x:v>
+        <x:v>4499</x:v>
       </x:c>
       <x:c r="P56" s="0">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="Q56" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R56" s="0">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S56" s="0">
-        <x:v>729</x:v>
+        <x:v>914</x:v>
       </x:c>
       <x:c r="T56" s="0">
-        <x:v>731</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="U56" s="0">
-        <x:v>731</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="V56" s="0">
-        <x:v>2941</x:v>
+        <x:v>3503</x:v>
       </x:c>
       <x:c r="W56" s="0">
-        <x:v>2946</x:v>
+        <x:v>3511</x:v>
       </x:c>
       <x:c r="X56" s="0">
-        <x:v>2944</x:v>
+        <x:v>3506</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:24">
@@ -4163,55 +4163,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F57" s="0">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G57" s="0">
-        <x:v>2.74</x:v>
+        <x:v>2.82</x:v>
       </x:c>
       <x:c r="H57" s="0">
-        <x:v>35.57</x:v>
+        <x:v>32.89</x:v>
       </x:c>
       <x:c r="K57" s="0">
-        <x:v>4.72</x:v>
+        <x:v>4.13</x:v>
       </x:c>
       <x:c r="L57" s="0">
-        <x:v>43.03</x:v>
+        <x:v>39.84</x:v>
       </x:c>
       <x:c r="M57" s="0">
-        <x:v>3753</x:v>
+        <x:v>4498</x:v>
       </x:c>
       <x:c r="N57" s="0">
-        <x:v>3757</x:v>
+        <x:v>4508</x:v>
       </x:c>
       <x:c r="O57" s="0">
-        <x:v>3754</x:v>
+        <x:v>4501</x:v>
       </x:c>
       <x:c r="P57" s="0">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="Q57" s="0">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R57" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="S57" s="0">
-        <x:v>732</x:v>
+        <x:v>916</x:v>
       </x:c>
       <x:c r="T57" s="0">
-        <x:v>733</x:v>
+        <x:v>918</x:v>
       </x:c>
       <x:c r="U57" s="0">
-        <x:v>733</x:v>
+        <x:v>918</x:v>
       </x:c>
       <x:c r="V57" s="0">
-        <x:v>2943</x:v>
+        <x:v>3504</x:v>
       </x:c>
       <x:c r="W57" s="0">
-        <x:v>2945</x:v>
+        <x:v>3509</x:v>
       </x:c>
       <x:c r="X57" s="0">
-        <x:v>2943</x:v>
+        <x:v>3505</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:24">
@@ -4228,55 +4228,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F58" s="0">
-        <x:v>64</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G58" s="0">
-        <x:v>2.9</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="H58" s="0">
-        <x:v>35.75</x:v>
+        <x:v>32.18</x:v>
       </x:c>
       <x:c r="K58" s="0">
-        <x:v>6.62</x:v>
+        <x:v>7.51</x:v>
       </x:c>
       <x:c r="L58" s="0">
-        <x:v>45.27</x:v>
+        <x:v>42.5</x:v>
       </x:c>
       <x:c r="M58" s="0">
-        <x:v>3757</x:v>
+        <x:v>4503</x:v>
       </x:c>
       <x:c r="N58" s="0">
-        <x:v>3761</x:v>
+        <x:v>4506</x:v>
       </x:c>
       <x:c r="O58" s="0">
-        <x:v>3759</x:v>
+        <x:v>4505</x:v>
       </x:c>
       <x:c r="P58" s="0">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="Q58" s="0">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="Q58" s="0">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="R58" s="0">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S58" s="0">
-        <x:v>734</x:v>
+        <x:v>919</x:v>
       </x:c>
       <x:c r="T58" s="0">
-        <x:v>735</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="U58" s="0">
-        <x:v>735</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="V58" s="0">
-        <x:v>2944</x:v>
+        <x:v>3507</x:v>
       </x:c>
       <x:c r="W58" s="0">
-        <x:v>2947</x:v>
+        <x:v>3509</x:v>
       </x:c>
       <x:c r="X58" s="0">
-        <x:v>2945</x:v>
+        <x:v>3507</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:24">
@@ -4293,55 +4293,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F59" s="0">
-        <x:v>70</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="G59" s="0">
-        <x:v>2.77</x:v>
+        <x:v>2.7</x:v>
       </x:c>
       <x:c r="H59" s="0">
-        <x:v>35.8</x:v>
+        <x:v>32.52</x:v>
       </x:c>
       <x:c r="K59" s="0">
-        <x:v>7.17</x:v>
+        <x:v>20.33</x:v>
       </x:c>
       <x:c r="L59" s="0">
-        <x:v>45.74</x:v>
+        <x:v>55.55</x:v>
       </x:c>
       <x:c r="M59" s="0">
-        <x:v>3758</x:v>
+        <x:v>4507</x:v>
       </x:c>
       <x:c r="N59" s="0">
-        <x:v>3762</x:v>
+        <x:v>4517</x:v>
       </x:c>
       <x:c r="O59" s="0">
-        <x:v>3761</x:v>
+        <x:v>4513</x:v>
       </x:c>
       <x:c r="P59" s="0">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="Q59" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R59" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="S59" s="0">
-        <x:v>736</x:v>
+        <x:v>921</x:v>
       </x:c>
       <x:c r="T59" s="0">
-        <x:v>739</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="U59" s="0">
-        <x:v>739</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="V59" s="0">
-        <x:v>2944</x:v>
+        <x:v>3508</x:v>
       </x:c>
       <x:c r="W59" s="0">
-        <x:v>2945</x:v>
+        <x:v>3513</x:v>
       </x:c>
       <x:c r="X59" s="0">
-        <x:v>2944</x:v>
+        <x:v>3510</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:24">
@@ -4358,55 +4358,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F60" s="0">
-        <x:v>96</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G60" s="0">
         <x:v>2.71</x:v>
       </x:c>
       <x:c r="H60" s="0">
-        <x:v>36.56</x:v>
+        <x:v>32.99</x:v>
       </x:c>
       <x:c r="K60" s="0">
-        <x:v>9.62</x:v>
+        <x:v>10.81</x:v>
       </x:c>
       <x:c r="L60" s="0">
-        <x:v>48.89</x:v>
+        <x:v>46.51</x:v>
       </x:c>
       <x:c r="M60" s="0">
-        <x:v>3765</x:v>
+        <x:v>4517</x:v>
       </x:c>
       <x:c r="N60" s="0">
-        <x:v>3768</x:v>
+        <x:v>4520</x:v>
       </x:c>
       <x:c r="O60" s="0">
-        <x:v>3766</x:v>
+        <x:v>4518</x:v>
       </x:c>
       <x:c r="P60" s="0">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q60" s="0">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="R60" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S60" s="0">
-        <x:v>740</x:v>
+        <x:v>924</x:v>
       </x:c>
       <x:c r="T60" s="0">
-        <x:v>741</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="U60" s="0">
-        <x:v>741</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="V60" s="0">
-        <x:v>2945</x:v>
+        <x:v>3510</x:v>
       </x:c>
       <x:c r="W60" s="0">
-        <x:v>2948</x:v>
+        <x:v>3512</x:v>
       </x:c>
       <x:c r="X60" s="0">
-        <x:v>2946</x:v>
+        <x:v>3511</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:24">
@@ -4423,55 +4423,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F61" s="0">
-        <x:v>76</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G61" s="0">
-        <x:v>2.67</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="H61" s="0">
-        <x:v>31.76</x:v>
+        <x:v>28.81</x:v>
       </x:c>
       <x:c r="K61" s="0">
-        <x:v>7.7</x:v>
+        <x:v>1.82</x:v>
       </x:c>
       <x:c r="L61" s="0">
-        <x:v>42.13</x:v>
+        <x:v>33.46</x:v>
       </x:c>
       <x:c r="M61" s="0">
-        <x:v>3765</x:v>
+        <x:v>4520</x:v>
       </x:c>
       <x:c r="N61" s="0">
-        <x:v>3774</x:v>
+        <x:v>4524</x:v>
       </x:c>
       <x:c r="O61" s="0">
-        <x:v>3769</x:v>
+        <x:v>4521</x:v>
       </x:c>
       <x:c r="P61" s="0">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q61" s="0">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="R61" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S61" s="0">
-        <x:v>742</x:v>
+        <x:v>926</x:v>
       </x:c>
       <x:c r="T61" s="0">
-        <x:v>743</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="U61" s="0">
-        <x:v>743</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="V61" s="0">
-        <x:v>2943</x:v>
+        <x:v>3512</x:v>
       </x:c>
       <x:c r="W61" s="0">
-        <x:v>2950</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="X61" s="0">
-        <x:v>2947</x:v>
+        <x:v>3513</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:24">
@@ -4488,55 +4488,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F62" s="0">
-        <x:v>42</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G62" s="0">
-        <x:v>2.78</x:v>
+        <x:v>2.64</x:v>
       </x:c>
       <x:c r="H62" s="0">
-        <x:v>30.12</x:v>
+        <x:v>27.63</x:v>
       </x:c>
       <x:c r="K62" s="0">
-        <x:v>4.12</x:v>
+        <x:v>2.37</x:v>
       </x:c>
       <x:c r="L62" s="0">
-        <x:v>37.02</x:v>
+        <x:v>32.64</x:v>
       </x:c>
       <x:c r="M62" s="0">
-        <x:v>3769</x:v>
+        <x:v>4521</x:v>
       </x:c>
       <x:c r="N62" s="0">
-        <x:v>3775</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="O62" s="0">
-        <x:v>3771</x:v>
+        <x:v>4526</x:v>
       </x:c>
       <x:c r="P62" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q62" s="0">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="R62" s="0">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="S62" s="0">
-        <x:v>744</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="T62" s="0">
-        <x:v>745</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="U62" s="0">
-        <x:v>745</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="V62" s="0">
-        <x:v>2946</x:v>
+        <x:v>3510</x:v>
       </x:c>
       <x:c r="W62" s="0">
-        <x:v>2948</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X62" s="0">
-        <x:v>2947</x:v>
+        <x:v>3515</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:24">
@@ -4553,55 +4553,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F63" s="0">
-        <x:v>289</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G63" s="0">
-        <x:v>2.74</x:v>
+        <x:v>2.71</x:v>
       </x:c>
       <x:c r="H63" s="0">
-        <x:v>35.48</x:v>
+        <x:v>32.61</x:v>
       </x:c>
       <x:c r="K63" s="0">
-        <x:v>29.56</x:v>
+        <x:v>11.71</x:v>
       </x:c>
       <x:c r="L63" s="0">
-        <x:v>67.78</x:v>
+        <x:v>47.03</x:v>
       </x:c>
       <x:c r="M63" s="0">
-        <x:v>3773</x:v>
+        <x:v>4524</x:v>
       </x:c>
       <x:c r="N63" s="0">
-        <x:v>3775</x:v>
+        <x:v>4527</x:v>
       </x:c>
       <x:c r="O63" s="0">
-        <x:v>3774</x:v>
+        <x:v>4526</x:v>
       </x:c>
       <x:c r="P63" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q63" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R63" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S63" s="0">
-        <x:v>746</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="T63" s="0">
-        <x:v>747</x:v>
+        <x:v>932</x:v>
       </x:c>
       <x:c r="U63" s="0">
-        <x:v>747</x:v>
+        <x:v>932</x:v>
       </x:c>
       <x:c r="V63" s="0">
-        <x:v>2947</x:v>
+        <x:v>3512</x:v>
       </x:c>
       <x:c r="W63" s="0">
-        <x:v>2949</x:v>
+        <x:v>3514</x:v>
       </x:c>
       <x:c r="X63" s="0">
-        <x:v>2948</x:v>
+        <x:v>3513</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:24">
@@ -4618,55 +4618,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F64" s="0">
-        <x:v>130</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G64" s="0">
-        <x:v>2.78</x:v>
+        <x:v>3.32</x:v>
       </x:c>
       <x:c r="H64" s="0">
-        <x:v>41.46</x:v>
+        <x:v>35.87</x:v>
       </x:c>
       <x:c r="K64" s="0">
-        <x:v>13.24</x:v>
+        <x:v>15.9</x:v>
       </x:c>
       <x:c r="L64" s="0">
-        <x:v>57.48</x:v>
+        <x:v>55.09</x:v>
       </x:c>
       <x:c r="M64" s="0">
-        <x:v>3663</x:v>
+        <x:v>4527</x:v>
       </x:c>
       <x:c r="N64" s="0">
-        <x:v>3780</x:v>
+        <x:v>4531</x:v>
       </x:c>
       <x:c r="O64" s="0">
-        <x:v>3778</x:v>
+        <x:v>4529</x:v>
       </x:c>
       <x:c r="P64" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q64" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R64" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S64" s="0">
-        <x:v>749</x:v>
+        <x:v>933</x:v>
       </x:c>
       <x:c r="T64" s="0">
-        <x:v>750</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="U64" s="0">
-        <x:v>750</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="V64" s="0">
-        <x:v>2833</x:v>
+        <x:v>3513</x:v>
       </x:c>
       <x:c r="W64" s="0">
-        <x:v>2951</x:v>
+        <x:v>3516</x:v>
       </x:c>
       <x:c r="X64" s="0">
-        <x:v>2948</x:v>
+        <x:v>3515</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:24">
@@ -4683,55 +4683,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F65" s="0">
-        <x:v>260</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G65" s="0">
-        <x:v>2.79</x:v>
+        <x:v>2.89</x:v>
       </x:c>
       <x:c r="H65" s="0">
-        <x:v>35.48</x:v>
+        <x:v>32.1</x:v>
       </x:c>
       <x:c r="K65" s="0">
-        <x:v>26.52</x:v>
+        <x:v>10.33</x:v>
       </x:c>
       <x:c r="L65" s="0">
-        <x:v>64.79</x:v>
+        <x:v>45.33</x:v>
       </x:c>
       <x:c r="M65" s="0">
-        <x:v>3778</x:v>
+        <x:v>4528</x:v>
       </x:c>
       <x:c r="N65" s="0">
-        <x:v>3782</x:v>
+        <x:v>4532</x:v>
       </x:c>
       <x:c r="O65" s="0">
-        <x:v>3781</x:v>
+        <x:v>4531</x:v>
       </x:c>
       <x:c r="P65" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q65" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R65" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S65" s="0">
-        <x:v>752</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="T65" s="0">
-        <x:v>753</x:v>
+        <x:v>935</x:v>
       </x:c>
       <x:c r="U65" s="0">
-        <x:v>753</x:v>
+        <x:v>935</x:v>
       </x:c>
       <x:c r="V65" s="0">
-        <x:v>2948</x:v>
+        <x:v>3512</x:v>
       </x:c>
       <x:c r="W65" s="0">
-        <x:v>2951</x:v>
+        <x:v>3516</x:v>
       </x:c>
       <x:c r="X65" s="0">
-        <x:v>2949</x:v>
+        <x:v>3515</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:24">
@@ -4748,55 +4748,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F66" s="0">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G66" s="0">
-        <x:v>3.53</x:v>
+        <x:v>2.88</x:v>
       </x:c>
       <x:c r="H66" s="0">
-        <x:v>36.57</x:v>
+        <x:v>33.82</x:v>
       </x:c>
       <x:c r="K66" s="0">
-        <x:v>4.15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L66" s="0">
-        <x:v>44.26</x:v>
+        <x:v>39.7</x:v>
       </x:c>
       <x:c r="M66" s="0">
-        <x:v>3791</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="N66" s="0">
-        <x:v>3805</x:v>
+        <x:v>4533</x:v>
       </x:c>
       <x:c r="O66" s="0">
-        <x:v>3804</x:v>
+        <x:v>4532</x:v>
       </x:c>
       <x:c r="P66" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q66" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R66" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S66" s="0">
-        <x:v>761</x:v>
+        <x:v>935</x:v>
       </x:c>
       <x:c r="T66" s="0">
-        <x:v>775</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="U66" s="0">
-        <x:v>775</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="V66" s="0">
-        <x:v>2948</x:v>
+        <x:v>3514</x:v>
       </x:c>
       <x:c r="W66" s="0">
-        <x:v>2951</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="X66" s="0">
-        <x:v>2950</x:v>
+        <x:v>3514</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:24">
@@ -4813,55 +4813,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F67" s="0">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G67" s="0">
-        <x:v>2.72</x:v>
+        <x:v>2.86</x:v>
       </x:c>
       <x:c r="H67" s="0">
-        <x:v>37.26</x:v>
+        <x:v>34.53</x:v>
       </x:c>
       <x:c r="K67" s="0">
-        <x:v>5.87</x:v>
+        <x:v>5.8</x:v>
       </x:c>
       <x:c r="L67" s="0">
-        <x:v>45.85</x:v>
+        <x:v>43.18</x:v>
       </x:c>
       <x:c r="M67" s="0">
-        <x:v>3804</x:v>
+        <x:v>4533</x:v>
       </x:c>
       <x:c r="N67" s="0">
-        <x:v>3807</x:v>
+        <x:v>4537</x:v>
       </x:c>
       <x:c r="O67" s="0">
-        <x:v>3806</x:v>
+        <x:v>4535</x:v>
       </x:c>
       <x:c r="P67" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q67" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R67" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S67" s="0">
-        <x:v>776</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="T67" s="0">
-        <x:v>777</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="U67" s="0">
-        <x:v>777</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="V67" s="0">
-        <x:v>2950</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W67" s="0">
-        <x:v>2952</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X67" s="0">
-        <x:v>2950</x:v>
+        <x:v>3515</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:24">
@@ -4878,55 +4878,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F68" s="0">
-        <x:v>168</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G68" s="0">
-        <x:v>2.69</x:v>
+        <x:v>2.76</x:v>
       </x:c>
       <x:c r="H68" s="0">
-        <x:v>34.87</x:v>
+        <x:v>31.63</x:v>
       </x:c>
       <x:c r="K68" s="0">
-        <x:v>16.84</x:v>
+        <x:v>12.31</x:v>
       </x:c>
       <x:c r="L68" s="0">
-        <x:v>54.4</x:v>
+        <x:v>46.7</x:v>
       </x:c>
       <x:c r="M68" s="0">
-        <x:v>3808</x:v>
+        <x:v>4534</x:v>
       </x:c>
       <x:c r="N68" s="0">
-        <x:v>3811</x:v>
+        <x:v>4539</x:v>
       </x:c>
       <x:c r="O68" s="0">
-        <x:v>3810</x:v>
+        <x:v>4537</x:v>
       </x:c>
       <x:c r="P68" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q68" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R68" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S68" s="0">
-        <x:v>777</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="T68" s="0">
-        <x:v>778</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="U68" s="0">
-        <x:v>778</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="V68" s="0">
-        <x:v>2952</x:v>
+        <x:v>3512</x:v>
       </x:c>
       <x:c r="W68" s="0">
-        <x:v>2953</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X68" s="0">
-        <x:v>2952</x:v>
+        <x:v>3516</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:24">
@@ -4943,55 +4943,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F69" s="0">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G69" s="0">
-        <x:v>2.76</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="H69" s="0">
-        <x:v>32.77</x:v>
+        <x:v>30.61</x:v>
       </x:c>
       <x:c r="K69" s="0">
-        <x:v>4.92</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="L69" s="0">
-        <x:v>40.45</x:v>
+        <x:v>37.81</x:v>
       </x:c>
       <x:c r="M69" s="0">
-        <x:v>3807</x:v>
+        <x:v>4535</x:v>
       </x:c>
       <x:c r="N69" s="0">
-        <x:v>3813</x:v>
+        <x:v>4537</x:v>
       </x:c>
       <x:c r="O69" s="0">
-        <x:v>3811</x:v>
+        <x:v>4536</x:v>
       </x:c>
       <x:c r="P69" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q69" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R69" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S69" s="0">
-        <x:v>779</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="T69" s="0">
-        <x:v>780</x:v>
+        <x:v>941</x:v>
       </x:c>
       <x:c r="U69" s="0">
-        <x:v>780</x:v>
+        <x:v>941</x:v>
       </x:c>
       <x:c r="V69" s="0">
-        <x:v>2949</x:v>
+        <x:v>3513</x:v>
       </x:c>
       <x:c r="W69" s="0">
-        <x:v>2954</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="X69" s="0">
-        <x:v>2952</x:v>
+        <x:v>3514</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:24">
@@ -5008,55 +5008,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F70" s="0">
-        <x:v>25</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G70" s="0">
-        <x:v>2.65</x:v>
+        <x:v>2.73</x:v>
       </x:c>
       <x:c r="H70" s="0">
-        <x:v>35.75</x:v>
+        <x:v>32.27</x:v>
       </x:c>
       <x:c r="K70" s="0">
-        <x:v>2.57</x:v>
+        <x:v>0.43</x:v>
       </x:c>
       <x:c r="L70" s="0">
-        <x:v>40.97</x:v>
+        <x:v>35.43</x:v>
       </x:c>
       <x:c r="M70" s="0">
-        <x:v>3810</x:v>
+        <x:v>4538</x:v>
       </x:c>
       <x:c r="N70" s="0">
-        <x:v>3812</x:v>
+        <x:v>4540</x:v>
       </x:c>
       <x:c r="O70" s="0">
-        <x:v>3810</x:v>
+        <x:v>4539</x:v>
       </x:c>
       <x:c r="P70" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q70" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R70" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S70" s="0">
-        <x:v>781</x:v>
+        <x:v>942</x:v>
       </x:c>
       <x:c r="T70" s="0">
-        <x:v>781</x:v>
+        <x:v>943</x:v>
       </x:c>
       <x:c r="U70" s="0">
-        <x:v>781</x:v>
+        <x:v>943</x:v>
       </x:c>
       <x:c r="V70" s="0">
-        <x:v>2950</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W70" s="0">
-        <x:v>2952</x:v>
+        <x:v>3516</x:v>
       </x:c>
       <x:c r="X70" s="0">
-        <x:v>2950</x:v>
+        <x:v>3515</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:24">
@@ -5073,55 +5073,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F71" s="0">
-        <x:v>241</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G71" s="0">
-        <x:v>2.88</x:v>
+        <x:v>2.71</x:v>
       </x:c>
       <x:c r="H71" s="0">
-        <x:v>36.6</x:v>
+        <x:v>33.76</x:v>
       </x:c>
       <x:c r="K71" s="0">
-        <x:v>24.71</x:v>
+        <x:v>9.32</x:v>
       </x:c>
       <x:c r="L71" s="0">
-        <x:v>64.18</x:v>
+        <x:v>45.79</x:v>
       </x:c>
       <x:c r="M71" s="0">
-        <x:v>3813</x:v>
+        <x:v>4538</x:v>
       </x:c>
       <x:c r="N71" s="0">
-        <x:v>3815</x:v>
+        <x:v>4542</x:v>
       </x:c>
       <x:c r="O71" s="0">
-        <x:v>3814</x:v>
+        <x:v>4541</x:v>
       </x:c>
       <x:c r="P71" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q71" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R71" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S71" s="0">
-        <x:v>782</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="T71" s="0">
-        <x:v>783</x:v>
+        <x:v>945</x:v>
       </x:c>
       <x:c r="U71" s="0">
-        <x:v>783</x:v>
+        <x:v>945</x:v>
       </x:c>
       <x:c r="V71" s="0">
-        <x:v>2952</x:v>
+        <x:v>3512</x:v>
       </x:c>
       <x:c r="W71" s="0">
-        <x:v>2953</x:v>
+        <x:v>3516</x:v>
       </x:c>
       <x:c r="X71" s="0">
-        <x:v>2952</x:v>
+        <x:v>3515</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:24">
@@ -5138,55 +5138,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F72" s="0">
-        <x:v>268</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="G72" s="0">
-        <x:v>2.62</x:v>
+        <x:v>2.76</x:v>
       </x:c>
       <x:c r="H72" s="0">
-        <x:v>36.66</x:v>
+        <x:v>33.62</x:v>
       </x:c>
       <x:c r="K72" s="0">
-        <x:v>27.69</x:v>
+        <x:v>26.13</x:v>
       </x:c>
       <x:c r="L72" s="0">
-        <x:v>66.97</x:v>
+        <x:v>62.51</x:v>
       </x:c>
       <x:c r="M72" s="0">
-        <x:v>3813</x:v>
+        <x:v>4541</x:v>
       </x:c>
       <x:c r="N72" s="0">
-        <x:v>3818</x:v>
+        <x:v>4544</x:v>
       </x:c>
       <x:c r="O72" s="0">
-        <x:v>3816</x:v>
+        <x:v>4543</x:v>
       </x:c>
       <x:c r="P72" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q72" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R72" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S72" s="0">
-        <x:v>784</x:v>
+        <x:v>947</x:v>
       </x:c>
       <x:c r="T72" s="0">
-        <x:v>786</x:v>
+        <x:v>948</x:v>
       </x:c>
       <x:c r="U72" s="0">
-        <x:v>786</x:v>
+        <x:v>948</x:v>
       </x:c>
       <x:c r="V72" s="0">
-        <x:v>2948</x:v>
+        <x:v>3514</x:v>
       </x:c>
       <x:c r="W72" s="0">
-        <x:v>2953</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="X72" s="0">
-        <x:v>2951</x:v>
+        <x:v>3514</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:24">
@@ -5203,55 +5203,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F73" s="0">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G73" s="0">
-        <x:v>2.86</x:v>
+        <x:v>2.88</x:v>
       </x:c>
       <x:c r="H73" s="0">
-        <x:v>36.41</x:v>
+        <x:v>33.77</x:v>
       </x:c>
       <x:c r="K73" s="0">
-        <x:v>9.94</x:v>
+        <x:v>7.21</x:v>
       </x:c>
       <x:c r="L73" s="0">
-        <x:v>49.21</x:v>
+        <x:v>43.86</x:v>
       </x:c>
       <x:c r="M73" s="0">
-        <x:v>3815</x:v>
+        <x:v>4544</x:v>
       </x:c>
       <x:c r="N73" s="0">
-        <x:v>3818</x:v>
+        <x:v>4547</x:v>
       </x:c>
       <x:c r="O73" s="0">
-        <x:v>3817</x:v>
+        <x:v>4546</x:v>
       </x:c>
       <x:c r="P73" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q73" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R73" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S73" s="0">
-        <x:v>786</x:v>
+        <x:v>948</x:v>
       </x:c>
       <x:c r="T73" s="0">
-        <x:v>787</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="U73" s="0">
-        <x:v>787</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="V73" s="0">
-        <x:v>2950</x:v>
+        <x:v>3514</x:v>
       </x:c>
       <x:c r="W73" s="0">
-        <x:v>2952</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X73" s="0">
-        <x:v>2950</x:v>
+        <x:v>3515</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:24">
@@ -5268,55 +5268,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F74" s="0">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G74" s="0">
-        <x:v>2.89</x:v>
+        <x:v>2.76</x:v>
       </x:c>
       <x:c r="H74" s="0">
-        <x:v>35.69</x:v>
+        <x:v>32.83</x:v>
       </x:c>
       <x:c r="K74" s="0">
-        <x:v>5.68</x:v>
+        <x:v>5.08</x:v>
       </x:c>
       <x:c r="L74" s="0">
-        <x:v>44.26</x:v>
+        <x:v>40.67</x:v>
       </x:c>
       <x:c r="M74" s="0">
-        <x:v>3817</x:v>
+        <x:v>4545</x:v>
       </x:c>
       <x:c r="N74" s="0">
-        <x:v>3819</x:v>
+        <x:v>4547</x:v>
       </x:c>
       <x:c r="O74" s="0">
-        <x:v>3819</x:v>
+        <x:v>4546</x:v>
       </x:c>
       <x:c r="P74" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q74" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R74" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S74" s="0">
-        <x:v>788</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="T74" s="0">
-        <x:v>789</x:v>
+        <x:v>951</x:v>
       </x:c>
       <x:c r="U74" s="0">
-        <x:v>789</x:v>
+        <x:v>951</x:v>
       </x:c>
       <x:c r="V74" s="0">
-        <x:v>2950</x:v>
+        <x:v>3514</x:v>
       </x:c>
       <x:c r="W74" s="0">
-        <x:v>2952</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="X74" s="0">
-        <x:v>2951</x:v>
+        <x:v>3514</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:24">
@@ -5333,55 +5333,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F75" s="0">
-        <x:v>47</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G75" s="0">
-        <x:v>2.76</x:v>
+        <x:v>2.87</x:v>
       </x:c>
       <x:c r="H75" s="0">
-        <x:v>35.81</x:v>
+        <x:v>32.87</x:v>
       </x:c>
       <x:c r="K75" s="0">
-        <x:v>4.77</x:v>
+        <x:v>7.26</x:v>
       </x:c>
       <x:c r="L75" s="0">
-        <x:v>43.34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M75" s="0">
-        <x:v>3818</x:v>
+        <x:v>4548</x:v>
       </x:c>
       <x:c r="N75" s="0">
-        <x:v>3821</x:v>
+        <x:v>4551</x:v>
       </x:c>
       <x:c r="O75" s="0">
-        <x:v>3820</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="P75" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q75" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R75" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S75" s="0">
-        <x:v>790</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="T75" s="0">
-        <x:v>791</x:v>
+        <x:v>953</x:v>
       </x:c>
       <x:c r="U75" s="0">
-        <x:v>791</x:v>
+        <x:v>953</x:v>
       </x:c>
       <x:c r="V75" s="0">
-        <x:v>2950</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W75" s="0">
-        <x:v>2951</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X75" s="0">
-        <x:v>2950</x:v>
+        <x:v>3516</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:24">
@@ -5398,55 +5398,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F76" s="0">
-        <x:v>159</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G76" s="0">
-        <x:v>2.85</x:v>
+        <x:v>2.73</x:v>
       </x:c>
       <x:c r="H76" s="0">
-        <x:v>37.01</x:v>
+        <x:v>33.52</x:v>
       </x:c>
       <x:c r="K76" s="0">
-        <x:v>16.29</x:v>
+        <x:v>12.51</x:v>
       </x:c>
       <x:c r="L76" s="0">
-        <x:v>56.15</x:v>
+        <x:v>48.76</x:v>
       </x:c>
       <x:c r="M76" s="0">
-        <x:v>3823</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="N76" s="0">
-        <x:v>3825</x:v>
+        <x:v>4554</x:v>
       </x:c>
       <x:c r="O76" s="0">
-        <x:v>3824</x:v>
+        <x:v>4553</x:v>
       </x:c>
       <x:c r="P76" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q76" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R76" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S76" s="0">
-        <x:v>792</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="T76" s="0">
-        <x:v>793</x:v>
+        <x:v>955</x:v>
       </x:c>
       <x:c r="U76" s="0">
-        <x:v>793</x:v>
+        <x:v>955</x:v>
       </x:c>
       <x:c r="V76" s="0">
-        <x:v>2951</x:v>
+        <x:v>3514</x:v>
       </x:c>
       <x:c r="W76" s="0">
-        <x:v>2953</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X76" s="0">
-        <x:v>2952</x:v>
+        <x:v>3516</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:24">
@@ -5463,55 +5463,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F77" s="0">
-        <x:v>59</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G77" s="0">
-        <x:v>2.75</x:v>
+        <x:v>2.76</x:v>
       </x:c>
       <x:c r="H77" s="0">
-        <x:v>31.28</x:v>
+        <x:v>28.89</x:v>
       </x:c>
       <x:c r="K77" s="0">
-        <x:v>5.94</x:v>
+        <x:v>6.99</x:v>
       </x:c>
       <x:c r="L77" s="0">
-        <x:v>39.97</x:v>
+        <x:v>38.64</x:v>
       </x:c>
       <x:c r="M77" s="0">
-        <x:v>3824</x:v>
+        <x:v>4552</x:v>
       </x:c>
       <x:c r="N77" s="0">
-        <x:v>3828</x:v>
+        <x:v>4555</x:v>
       </x:c>
       <x:c r="O77" s="0">
-        <x:v>3827</x:v>
+        <x:v>4554</x:v>
       </x:c>
       <x:c r="P77" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q77" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R77" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S77" s="0">
-        <x:v>795</x:v>
+        <x:v>957</x:v>
       </x:c>
       <x:c r="T77" s="0">
-        <x:v>796</x:v>
+        <x:v>958</x:v>
       </x:c>
       <x:c r="U77" s="0">
-        <x:v>796</x:v>
+        <x:v>958</x:v>
       </x:c>
       <x:c r="V77" s="0">
-        <x:v>2949</x:v>
+        <x:v>3514</x:v>
       </x:c>
       <x:c r="W77" s="0">
-        <x:v>2953</x:v>
+        <x:v>3516</x:v>
       </x:c>
       <x:c r="X77" s="0">
-        <x:v>2952</x:v>
+        <x:v>3515</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:24">
@@ -5528,55 +5528,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F78" s="0">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G78" s="0">
-        <x:v>2.77</x:v>
+        <x:v>2.66</x:v>
       </x:c>
       <x:c r="H78" s="0">
-        <x:v>30.44</x:v>
+        <x:v>27.86</x:v>
       </x:c>
       <x:c r="K78" s="0">
-        <x:v>2.63</x:v>
+        <x:v>2.41</x:v>
       </x:c>
       <x:c r="L78" s="0">
-        <x:v>35.84</x:v>
+        <x:v>32.93</x:v>
       </x:c>
       <x:c r="M78" s="0">
-        <x:v>3826</x:v>
+        <x:v>4556</x:v>
       </x:c>
       <x:c r="N78" s="0">
-        <x:v>3829</x:v>
+        <x:v>4559</x:v>
       </x:c>
       <x:c r="O78" s="0">
-        <x:v>3828</x:v>
+        <x:v>4558</x:v>
       </x:c>
       <x:c r="P78" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q78" s="0">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="R78" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S78" s="0">
-        <x:v>796</x:v>
+        <x:v>959</x:v>
       </x:c>
       <x:c r="T78" s="0">
-        <x:v>798</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="U78" s="0">
-        <x:v>798</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="V78" s="0">
-        <x:v>2951</x:v>
+        <x:v>3516</x:v>
       </x:c>
       <x:c r="W78" s="0">
-        <x:v>2952</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X78" s="0">
-        <x:v>2951</x:v>
+        <x:v>3516</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:24">
@@ -5593,55 +5593,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F79" s="0">
-        <x:v>272</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="G79" s="0">
-        <x:v>2.67</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="H79" s="0">
-        <x:v>36.83</x:v>
+        <x:v>32.69</x:v>
       </x:c>
       <x:c r="K79" s="0">
-        <x:v>28.06</x:v>
+        <x:v>30.75</x:v>
       </x:c>
       <x:c r="L79" s="0">
-        <x:v>67.55</x:v>
+        <x:v>66.23</x:v>
       </x:c>
       <x:c r="M79" s="0">
-        <x:v>3830</x:v>
+        <x:v>4558</x:v>
       </x:c>
       <x:c r="N79" s="0">
-        <x:v>3834</x:v>
+        <x:v>4562</x:v>
       </x:c>
       <x:c r="O79" s="0">
-        <x:v>3833</x:v>
+        <x:v>4560</x:v>
       </x:c>
       <x:c r="P79" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q79" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R79" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S79" s="0">
-        <x:v>799</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="T79" s="0">
-        <x:v>800</x:v>
+        <x:v>963</x:v>
       </x:c>
       <x:c r="U79" s="0">
-        <x:v>800</x:v>
+        <x:v>963</x:v>
       </x:c>
       <x:c r="V79" s="0">
-        <x:v>2952</x:v>
+        <x:v>3514</x:v>
       </x:c>
       <x:c r="W79" s="0">
-        <x:v>2955</x:v>
+        <x:v>3518</x:v>
       </x:c>
       <x:c r="X79" s="0">
-        <x:v>2954</x:v>
+        <x:v>3516</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:24">
@@ -5658,55 +5658,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F80" s="0">
-        <x:v>121</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="G80" s="0">
-        <x:v>2.85</x:v>
+        <x:v>2.69</x:v>
       </x:c>
       <x:c r="H80" s="0">
-        <x:v>38.87</x:v>
+        <x:v>36.43</x:v>
       </x:c>
       <x:c r="K80" s="0">
-        <x:v>12.22</x:v>
+        <x:v>20.43</x:v>
       </x:c>
       <x:c r="L80" s="0">
-        <x:v>53.94</x:v>
+        <x:v>59.55</x:v>
       </x:c>
       <x:c r="M80" s="0">
-        <x:v>3831</x:v>
+        <x:v>4559</x:v>
       </x:c>
       <x:c r="N80" s="0">
-        <x:v>3836</x:v>
+        <x:v>4562</x:v>
       </x:c>
       <x:c r="O80" s="0">
-        <x:v>3834</x:v>
+        <x:v>4561</x:v>
       </x:c>
       <x:c r="P80" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q80" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R80" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S80" s="0">
-        <x:v>801</x:v>
+        <x:v>964</x:v>
       </x:c>
       <x:c r="T80" s="0">
-        <x:v>802</x:v>
+        <x:v>965</x:v>
       </x:c>
       <x:c r="U80" s="0">
-        <x:v>802</x:v>
+        <x:v>965</x:v>
       </x:c>
       <x:c r="V80" s="0">
-        <x:v>2951</x:v>
+        <x:v>3514</x:v>
       </x:c>
       <x:c r="W80" s="0">
-        <x:v>2955</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X80" s="0">
-        <x:v>2954</x:v>
+        <x:v>3515</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:24">
@@ -5723,55 +5723,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F81" s="0">
-        <x:v>185</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G81" s="0">
-        <x:v>2.74</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="H81" s="0">
-        <x:v>35.11</x:v>
+        <x:v>32.08</x:v>
       </x:c>
       <x:c r="K81" s="0">
-        <x:v>18.91</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="L81" s="0">
-        <x:v>56.75</x:v>
+        <x:v>38.01</x:v>
       </x:c>
       <x:c r="M81" s="0">
-        <x:v>3834</x:v>
+        <x:v>4563</x:v>
       </x:c>
       <x:c r="N81" s="0">
-        <x:v>3836</x:v>
+        <x:v>4565</x:v>
       </x:c>
       <x:c r="O81" s="0">
-        <x:v>3835</x:v>
+        <x:v>4565</x:v>
       </x:c>
       <x:c r="P81" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q81" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R81" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S81" s="0">
-        <x:v>803</x:v>
+        <x:v>966</x:v>
       </x:c>
       <x:c r="T81" s="0">
-        <x:v>804</x:v>
+        <x:v>967</x:v>
       </x:c>
       <x:c r="U81" s="0">
-        <x:v>804</x:v>
+        <x:v>967</x:v>
       </x:c>
       <x:c r="V81" s="0">
-        <x:v>2952</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W81" s="0">
-        <x:v>2953</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X81" s="0">
-        <x:v>2952</x:v>
+        <x:v>3516</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:24">
@@ -5788,55 +5788,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F82" s="0">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G82" s="0">
         <x:v>2.77</x:v>
       </x:c>
       <x:c r="H82" s="0">
-        <x:v>36.72</x:v>
+        <x:v>33.47</x:v>
       </x:c>
       <x:c r="K82" s="0">
-        <x:v>6.3</x:v>
+        <x:v>3.52</x:v>
       </x:c>
       <x:c r="L82" s="0">
-        <x:v>45.8</x:v>
+        <x:v>39.76</x:v>
       </x:c>
       <x:c r="M82" s="0">
-        <x:v>3837</x:v>
+        <x:v>4564</x:v>
       </x:c>
       <x:c r="N82" s="0">
-        <x:v>3840</x:v>
+        <x:v>4567</x:v>
       </x:c>
       <x:c r="O82" s="0">
-        <x:v>3839</x:v>
+        <x:v>4565</x:v>
       </x:c>
       <x:c r="P82" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q82" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R82" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S82" s="0">
-        <x:v>805</x:v>
+        <x:v>968</x:v>
       </x:c>
       <x:c r="T82" s="0">
-        <x:v>807</x:v>
+        <x:v>969</x:v>
       </x:c>
       <x:c r="U82" s="0">
-        <x:v>807</x:v>
+        <x:v>969</x:v>
       </x:c>
       <x:c r="V82" s="0">
-        <x:v>2952</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W82" s="0">
-        <x:v>2955</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X82" s="0">
-        <x:v>2953</x:v>
+        <x:v>3515</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:24">
@@ -5853,55 +5853,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F83" s="0">
-        <x:v>46</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G83" s="0">
-        <x:v>2.78</x:v>
+        <x:v>2.68</x:v>
       </x:c>
       <x:c r="H83" s="0">
-        <x:v>39.01</x:v>
+        <x:v>33.95</x:v>
       </x:c>
       <x:c r="K83" s="0">
-        <x:v>4.5</x:v>
+        <x:v>5.51</x:v>
       </x:c>
       <x:c r="L83" s="0">
-        <x:v>46.29</x:v>
+        <x:v>42.14</x:v>
       </x:c>
       <x:c r="M83" s="0">
-        <x:v>3838</x:v>
+        <x:v>4568</x:v>
       </x:c>
       <x:c r="N83" s="0">
-        <x:v>3841</x:v>
+        <x:v>4572</x:v>
       </x:c>
       <x:c r="O83" s="0">
-        <x:v>3840</x:v>
+        <x:v>4570</x:v>
       </x:c>
       <x:c r="P83" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q83" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R83" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S83" s="0">
-        <x:v>808</x:v>
+        <x:v>970</x:v>
       </x:c>
       <x:c r="T83" s="0">
-        <x:v>809</x:v>
+        <x:v>972</x:v>
       </x:c>
       <x:c r="U83" s="0">
-        <x:v>809</x:v>
+        <x:v>972</x:v>
       </x:c>
       <x:c r="V83" s="0">
-        <x:v>2951</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="W83" s="0">
-        <x:v>2953</x:v>
+        <x:v>3518</x:v>
       </x:c>
       <x:c r="X83" s="0">
-        <x:v>2952</x:v>
+        <x:v>3517</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:24">
@@ -5918,55 +5918,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F84" s="0">
-        <x:v>92</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G84" s="0">
-        <x:v>2.69</x:v>
+        <x:v>2.8</x:v>
       </x:c>
       <x:c r="H84" s="0">
-        <x:v>35</x:v>
+        <x:v>32.11</x:v>
       </x:c>
       <x:c r="K84" s="0">
-        <x:v>9.4</x:v>
+        <x:v>6.53</x:v>
       </x:c>
       <x:c r="L84" s="0">
-        <x:v>47.09</x:v>
+        <x:v>41.45</x:v>
       </x:c>
       <x:c r="M84" s="0">
-        <x:v>3842</x:v>
+        <x:v>4570</x:v>
       </x:c>
       <x:c r="N84" s="0">
-        <x:v>3845</x:v>
+        <x:v>4573</x:v>
       </x:c>
       <x:c r="O84" s="0">
-        <x:v>3844</x:v>
+        <x:v>4573</x:v>
       </x:c>
       <x:c r="P84" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q84" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R84" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S84" s="0">
-        <x:v>810</x:v>
+        <x:v>973</x:v>
       </x:c>
       <x:c r="T84" s="0">
-        <x:v>811</x:v>
+        <x:v>974</x:v>
       </x:c>
       <x:c r="U84" s="0">
-        <x:v>811</x:v>
+        <x:v>974</x:v>
       </x:c>
       <x:c r="V84" s="0">
-        <x:v>2953</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W84" s="0">
-        <x:v>2955</x:v>
+        <x:v>3518</x:v>
       </x:c>
       <x:c r="X84" s="0">
-        <x:v>2954</x:v>
+        <x:v>3517</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:24">
@@ -5983,55 +5983,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F85" s="0">
-        <x:v>28</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G85" s="0">
-        <x:v>2.75</x:v>
+        <x:v>2.73</x:v>
       </x:c>
       <x:c r="H85" s="0">
-        <x:v>33.49</x:v>
+        <x:v>30.24</x:v>
       </x:c>
       <x:c r="K85" s="0">
-        <x:v>2.86</x:v>
+        <x:v>5.49</x:v>
       </x:c>
       <x:c r="L85" s="0">
-        <x:v>39.1</x:v>
+        <x:v>38.46</x:v>
       </x:c>
       <x:c r="M85" s="0">
-        <x:v>3839</x:v>
+        <x:v>4571</x:v>
       </x:c>
       <x:c r="N85" s="0">
-        <x:v>3847</x:v>
+        <x:v>4574</x:v>
       </x:c>
       <x:c r="O85" s="0">
-        <x:v>3844</x:v>
+        <x:v>4572</x:v>
       </x:c>
       <x:c r="P85" s="0">
-        <x:v>75</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q85" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R85" s="0">
-        <x:v>77</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S85" s="0">
-        <x:v>813</x:v>
+        <x:v>976</x:v>
       </x:c>
       <x:c r="T85" s="0">
-        <x:v>814</x:v>
+        <x:v>977</x:v>
       </x:c>
       <x:c r="U85" s="0">
-        <x:v>814</x:v>
+        <x:v>977</x:v>
       </x:c>
       <x:c r="V85" s="0">
-        <x:v>2950</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W85" s="0">
-        <x:v>2955</x:v>
+        <x:v>3516</x:v>
       </x:c>
       <x:c r="X85" s="0">
-        <x:v>2953</x:v>
+        <x:v>3515</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:24">
@@ -6048,55 +6048,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F86" s="0">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G86" s="0">
-        <x:v>2.6</x:v>
+        <x:v>2.79</x:v>
       </x:c>
       <x:c r="H86" s="0">
-        <x:v>34.9</x:v>
+        <x:v>32.38</x:v>
       </x:c>
       <x:c r="K86" s="0">
-        <x:v>1.89</x:v>
+        <x:v>1.45</x:v>
       </x:c>
       <x:c r="L86" s="0">
-        <x:v>39.39</x:v>
+        <x:v>36.61</x:v>
       </x:c>
       <x:c r="M86" s="0">
-        <x:v>3846</x:v>
+        <x:v>4575</x:v>
       </x:c>
       <x:c r="N86" s="0">
-        <x:v>3848</x:v>
+        <x:v>4578</x:v>
       </x:c>
       <x:c r="O86" s="0">
-        <x:v>3847</x:v>
+        <x:v>4576</x:v>
       </x:c>
       <x:c r="P86" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q86" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R86" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S86" s="0">
-        <x:v>815</x:v>
+        <x:v>978</x:v>
       </x:c>
       <x:c r="T86" s="0">
-        <x:v>816</x:v>
+        <x:v>979</x:v>
       </x:c>
       <x:c r="U86" s="0">
-        <x:v>816</x:v>
+        <x:v>979</x:v>
       </x:c>
       <x:c r="V86" s="0">
-        <x:v>2952</x:v>
+        <x:v>3516</x:v>
       </x:c>
       <x:c r="W86" s="0">
-        <x:v>2954</x:v>
+        <x:v>3518</x:v>
       </x:c>
       <x:c r="X86" s="0">
-        <x:v>2952</x:v>
+        <x:v>3517</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:24">
@@ -6113,55 +6113,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F87" s="0">
-        <x:v>152</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G87" s="0">
-        <x:v>2.7</x:v>
+        <x:v>2.81</x:v>
       </x:c>
       <x:c r="H87" s="0">
-        <x:v>36.65</x:v>
+        <x:v>33.95</x:v>
       </x:c>
       <x:c r="K87" s="0">
-        <x:v>15.29</x:v>
+        <x:v>19.99</x:v>
       </x:c>
       <x:c r="L87" s="0">
-        <x:v>54.64</x:v>
+        <x:v>56.75</x:v>
       </x:c>
       <x:c r="M87" s="0">
-        <x:v>3851</x:v>
+        <x:v>4577</x:v>
       </x:c>
       <x:c r="N87" s="0">
-        <x:v>3853</x:v>
+        <x:v>4582</x:v>
       </x:c>
       <x:c r="O87" s="0">
-        <x:v>3852</x:v>
+        <x:v>4580</x:v>
       </x:c>
       <x:c r="P87" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q87" s="0">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R87" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S87" s="0">
-        <x:v>817</x:v>
+        <x:v>980</x:v>
       </x:c>
       <x:c r="T87" s="0">
-        <x:v>819</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="U87" s="0">
-        <x:v>819</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="V87" s="0">
-        <x:v>2954</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W87" s="0">
-        <x:v>2955</x:v>
+        <x:v>3520</x:v>
       </x:c>
       <x:c r="X87" s="0">
-        <x:v>2954</x:v>
+        <x:v>3517</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:24">
@@ -6178,55 +6178,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F88" s="0">
-        <x:v>274</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="G88" s="0">
-        <x:v>2.75</x:v>
+        <x:v>2.73</x:v>
       </x:c>
       <x:c r="H88" s="0">
-        <x:v>36.77</x:v>
+        <x:v>33.17</x:v>
       </x:c>
       <x:c r="K88" s="0">
-        <x:v>27.49</x:v>
+        <x:v>24.42</x:v>
       </x:c>
       <x:c r="L88" s="0">
-        <x:v>67.01</x:v>
+        <x:v>60.33</x:v>
       </x:c>
       <x:c r="M88" s="0">
-        <x:v>3850</x:v>
+        <x:v>4578</x:v>
       </x:c>
       <x:c r="N88" s="0">
-        <x:v>3855</x:v>
+        <x:v>4582</x:v>
       </x:c>
       <x:c r="O88" s="0">
-        <x:v>3853</x:v>
+        <x:v>4581</x:v>
       </x:c>
       <x:c r="P88" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q88" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R88" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S88" s="0">
-        <x:v>820</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="T88" s="0">
-        <x:v>821</x:v>
+        <x:v>984</x:v>
       </x:c>
       <x:c r="U88" s="0">
-        <x:v>821</x:v>
+        <x:v>984</x:v>
       </x:c>
       <x:c r="V88" s="0">
-        <x:v>2950</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W88" s="0">
-        <x:v>2955</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X88" s="0">
-        <x:v>2953</x:v>
+        <x:v>3516</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:24">
@@ -6243,55 +6243,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F89" s="0">
-        <x:v>93</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G89" s="0">
-        <x:v>2.78</x:v>
+        <x:v>2.63</x:v>
       </x:c>
       <x:c r="H89" s="0">
-        <x:v>37.13</x:v>
+        <x:v>33.55</x:v>
       </x:c>
       <x:c r="K89" s="0">
-        <x:v>9.38</x:v>
+        <x:v>5.78</x:v>
       </x:c>
       <x:c r="L89" s="0">
-        <x:v>49.29</x:v>
+        <x:v>41.97</x:v>
       </x:c>
       <x:c r="M89" s="0">
-        <x:v>3853</x:v>
+        <x:v>4582</x:v>
       </x:c>
       <x:c r="N89" s="0">
-        <x:v>3856</x:v>
+        <x:v>4585</x:v>
       </x:c>
       <x:c r="O89" s="0">
-        <x:v>3855</x:v>
+        <x:v>4584</x:v>
       </x:c>
       <x:c r="P89" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q89" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R89" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S89" s="0">
-        <x:v>822</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="T89" s="0">
-        <x:v>824</x:v>
+        <x:v>986</x:v>
       </x:c>
       <x:c r="U89" s="0">
-        <x:v>824</x:v>
+        <x:v>986</x:v>
       </x:c>
       <x:c r="V89" s="0">
-        <x:v>2952</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W89" s="0">
-        <x:v>2954</x:v>
+        <x:v>3518</x:v>
       </x:c>
       <x:c r="X89" s="0">
-        <x:v>2952</x:v>
+        <x:v>3517</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:24">
@@ -6308,55 +6308,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F90" s="0">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G90" s="0">
-        <x:v>2.73</x:v>
+        <x:v>2.56</x:v>
       </x:c>
       <x:c r="H90" s="0">
-        <x:v>35.26</x:v>
+        <x:v>32.8</x:v>
       </x:c>
       <x:c r="K90" s="0">
-        <x:v>9.42</x:v>
+        <x:v>8.08</x:v>
       </x:c>
       <x:c r="L90" s="0">
-        <x:v>47.41</x:v>
+        <x:v>43.44</x:v>
       </x:c>
       <x:c r="M90" s="0">
-        <x:v>3856</x:v>
+        <x:v>4583</x:v>
       </x:c>
       <x:c r="N90" s="0">
-        <x:v>3858</x:v>
+        <x:v>4586</x:v>
       </x:c>
       <x:c r="O90" s="0">
-        <x:v>3858</x:v>
+        <x:v>4585</x:v>
       </x:c>
       <x:c r="P90" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q90" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R90" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S90" s="0">
-        <x:v>825</x:v>
+        <x:v>987</x:v>
       </x:c>
       <x:c r="T90" s="0">
-        <x:v>825</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="U90" s="0">
-        <x:v>825</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="V90" s="0">
-        <x:v>2952</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W90" s="0">
-        <x:v>2954</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X90" s="0">
-        <x:v>2953</x:v>
+        <x:v>3515</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:24">
@@ -6373,55 +6373,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F91" s="0">
-        <x:v>92</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G91" s="0">
-        <x:v>2.63</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H91" s="0">
-        <x:v>35.48</x:v>
+        <x:v>32.92</x:v>
       </x:c>
       <x:c r="K91" s="0">
-        <x:v>8.92</x:v>
+        <x:v>3.97</x:v>
       </x:c>
       <x:c r="L91" s="0">
-        <x:v>47.03</x:v>
+        <x:v>39.56</x:v>
       </x:c>
       <x:c r="M91" s="0">
-        <x:v>3857</x:v>
+        <x:v>4587</x:v>
       </x:c>
       <x:c r="N91" s="0">
-        <x:v>3860</x:v>
+        <x:v>4590</x:v>
       </x:c>
       <x:c r="O91" s="0">
-        <x:v>3858</x:v>
+        <x:v>4589</x:v>
       </x:c>
       <x:c r="P91" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q91" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R91" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S91" s="0">
-        <x:v>826</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="T91" s="0">
-        <x:v>827</x:v>
+        <x:v>991</x:v>
       </x:c>
       <x:c r="U91" s="0">
-        <x:v>827</x:v>
+        <x:v>991</x:v>
       </x:c>
       <x:c r="V91" s="0">
-        <x:v>2952</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="W91" s="0">
-        <x:v>2954</x:v>
+        <x:v>3518</x:v>
       </x:c>
       <x:c r="X91" s="0">
-        <x:v>2952</x:v>
+        <x:v>3517</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:24">
@@ -6438,55 +6438,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F92" s="0">
-        <x:v>149</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G92" s="0">
-        <x:v>2.71</x:v>
+        <x:v>2.83</x:v>
       </x:c>
       <x:c r="H92" s="0">
-        <x:v>36.29</x:v>
+        <x:v>33.49</x:v>
       </x:c>
       <x:c r="K92" s="0">
-        <x:v>14.95</x:v>
+        <x:v>7.87</x:v>
       </x:c>
       <x:c r="L92" s="0">
-        <x:v>53.95</x:v>
+        <x:v>44.19</x:v>
       </x:c>
       <x:c r="M92" s="0">
-        <x:v>3861</x:v>
+        <x:v>4590</x:v>
       </x:c>
       <x:c r="N92" s="0">
-        <x:v>3864</x:v>
+        <x:v>4594</x:v>
       </x:c>
       <x:c r="O92" s="0">
-        <x:v>3863</x:v>
+        <x:v>4592</x:v>
       </x:c>
       <x:c r="P92" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q92" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R92" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S92" s="0">
-        <x:v>828</x:v>
+        <x:v>992</x:v>
       </x:c>
       <x:c r="T92" s="0">
-        <x:v>830</x:v>
+        <x:v>993</x:v>
       </x:c>
       <x:c r="U92" s="0">
-        <x:v>830</x:v>
+        <x:v>993</x:v>
       </x:c>
       <x:c r="V92" s="0">
-        <x:v>2954</x:v>
+        <x:v>3516</x:v>
       </x:c>
       <x:c r="W92" s="0">
-        <x:v>2956</x:v>
+        <x:v>3520</x:v>
       </x:c>
       <x:c r="X92" s="0">
-        <x:v>2954</x:v>
+        <x:v>3518</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:24">
@@ -6503,55 +6503,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F93" s="0">
-        <x:v>100</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G93" s="0">
-        <x:v>2.73</x:v>
+        <x:v>2.77</x:v>
       </x:c>
       <x:c r="H93" s="0">
-        <x:v>31.92</x:v>
+        <x:v>28.63</x:v>
       </x:c>
       <x:c r="K93" s="0">
-        <x:v>9.87</x:v>
+        <x:v>13.92</x:v>
       </x:c>
       <x:c r="L93" s="0">
-        <x:v>44.52</x:v>
+        <x:v>45.32</x:v>
       </x:c>
       <x:c r="M93" s="0">
-        <x:v>3862</x:v>
+        <x:v>4591</x:v>
       </x:c>
       <x:c r="N93" s="0">
-        <x:v>3866</x:v>
+        <x:v>4594</x:v>
       </x:c>
       <x:c r="O93" s="0">
-        <x:v>3865</x:v>
+        <x:v>4592</x:v>
       </x:c>
       <x:c r="P93" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q93" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R93" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S93" s="0">
-        <x:v>831</x:v>
+        <x:v>994</x:v>
       </x:c>
       <x:c r="T93" s="0">
-        <x:v>832</x:v>
+        <x:v>996</x:v>
       </x:c>
       <x:c r="U93" s="0">
-        <x:v>832</x:v>
+        <x:v>996</x:v>
       </x:c>
       <x:c r="V93" s="0">
-        <x:v>2951</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W93" s="0">
-        <x:v>2956</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X93" s="0">
-        <x:v>2955</x:v>
+        <x:v>3516</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:24">
@@ -6568,55 +6568,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F94" s="0">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G94" s="0">
-        <x:v>2.71</x:v>
+        <x:v>2.78</x:v>
       </x:c>
       <x:c r="H94" s="0">
-        <x:v>30.14</x:v>
+        <x:v>28.54</x:v>
       </x:c>
       <x:c r="K94" s="0">
-        <x:v>2.6</x:v>
+        <x:v>2.34</x:v>
       </x:c>
       <x:c r="L94" s="0">
-        <x:v>35.45</x:v>
+        <x:v>33.66</x:v>
       </x:c>
       <x:c r="M94" s="0">
-        <x:v>3864</x:v>
+        <x:v>4595</x:v>
       </x:c>
       <x:c r="N94" s="0">
-        <x:v>3867</x:v>
+        <x:v>4598</x:v>
       </x:c>
       <x:c r="O94" s="0">
-        <x:v>3866</x:v>
+        <x:v>4596</x:v>
       </x:c>
       <x:c r="P94" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q94" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R94" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S94" s="0">
-        <x:v>833</x:v>
+        <x:v>997</x:v>
       </x:c>
       <x:c r="T94" s="0">
-        <x:v>834</x:v>
+        <x:v>998</x:v>
       </x:c>
       <x:c r="U94" s="0">
-        <x:v>834</x:v>
+        <x:v>998</x:v>
       </x:c>
       <x:c r="V94" s="0">
-        <x:v>2953</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="W94" s="0">
-        <x:v>2954</x:v>
+        <x:v>3518</x:v>
       </x:c>
       <x:c r="X94" s="0">
-        <x:v>2953</x:v>
+        <x:v>3517</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:24">
@@ -6633,55 +6633,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F95" s="0">
-        <x:v>257</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G95" s="0">
-        <x:v>2.69</x:v>
+        <x:v>2.67</x:v>
       </x:c>
       <x:c r="H95" s="0">
-        <x:v>35.94</x:v>
+        <x:v>32.71</x:v>
       </x:c>
       <x:c r="K95" s="0">
-        <x:v>25.98</x:v>
+        <x:v>9.29</x:v>
       </x:c>
       <x:c r="L95" s="0">
-        <x:v>64.61</x:v>
+        <x:v>44.67</x:v>
       </x:c>
       <x:c r="M95" s="0">
-        <x:v>3868</x:v>
+        <x:v>4597</x:v>
       </x:c>
       <x:c r="N95" s="0">
-        <x:v>3872</x:v>
+        <x:v>4601</x:v>
       </x:c>
       <x:c r="O95" s="0">
-        <x:v>3871</x:v>
+        <x:v>4599</x:v>
       </x:c>
       <x:c r="P95" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q95" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R95" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S95" s="0">
-        <x:v>835</x:v>
+        <x:v>999</x:v>
       </x:c>
       <x:c r="T95" s="0">
-        <x:v>837</x:v>
+        <x:v>1001</x:v>
       </x:c>
       <x:c r="U95" s="0">
-        <x:v>837</x:v>
+        <x:v>1001</x:v>
       </x:c>
       <x:c r="V95" s="0">
-        <x:v>2954</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W95" s="0">
-        <x:v>2956</x:v>
+        <x:v>3519</x:v>
       </x:c>
       <x:c r="X95" s="0">
-        <x:v>2955</x:v>
+        <x:v>3518</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:24">
@@ -6698,55 +6698,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F96" s="0">
-        <x:v>123</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G96" s="0">
-        <x:v>2.94</x:v>
+        <x:v>2.76</x:v>
       </x:c>
       <x:c r="H96" s="0">
-        <x:v>39.67</x:v>
+        <x:v>36.01</x:v>
       </x:c>
       <x:c r="K96" s="0">
-        <x:v>12.37</x:v>
+        <x:v>18.19</x:v>
       </x:c>
       <x:c r="L96" s="0">
-        <x:v>54.98</x:v>
+        <x:v>56.96</x:v>
       </x:c>
       <x:c r="M96" s="0">
-        <x:v>3870</x:v>
+        <x:v>4598</x:v>
       </x:c>
       <x:c r="N96" s="0">
-        <x:v>3874</x:v>
+        <x:v>4601</x:v>
       </x:c>
       <x:c r="O96" s="0">
-        <x:v>3873</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="P96" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q96" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R96" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S96" s="0">
-        <x:v>838</x:v>
+        <x:v>1002</x:v>
       </x:c>
       <x:c r="T96" s="0">
-        <x:v>839</x:v>
+        <x:v>1003</x:v>
       </x:c>
       <x:c r="U96" s="0">
-        <x:v>839</x:v>
+        <x:v>1003</x:v>
       </x:c>
       <x:c r="V96" s="0">
-        <x:v>2952</x:v>
+        <x:v>3515</x:v>
       </x:c>
       <x:c r="W96" s="0">
-        <x:v>2956</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="X96" s="0">
-        <x:v>2955</x:v>
+        <x:v>3516</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:24">
@@ -6763,55 +6763,55 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="F97" s="0">
-        <x:v>217</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G97" s="0">
-        <x:v>2.85</x:v>
+        <x:v>2.76</x:v>
       </x:c>
       <x:c r="H97" s="0">
-        <x:v>35.93</x:v>
+        <x:v>32.67</x:v>
       </x:c>
       <x:c r="K97" s="0">
-        <x:v>22.12</x:v>
+        <x:v>9.32</x:v>
       </x:c>
       <x:c r="L97" s="0">
-        <x:v>60.9</x:v>
+        <x:v>44.76</x:v>
       </x:c>
       <x:c r="M97" s="0">
-        <x:v>3872</x:v>
+        <x:v>4602</x:v>
       </x:c>
       <x:c r="N97" s="0">
-        <x:v>3876</x:v>
+        <x:v>4605</x:v>
       </x:c>
       <x:c r="O97" s="0">
-        <x:v>3874</x:v>
+        <x:v>4604</x:v>
       </x:c>
       <x:c r="P97" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q97" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="R97" s="0">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S97" s="0">
-        <x:v>840</x:v>
+        <x:v>1004</x:v>
       </x:c>
       <x:c r="T97" s="0">
-        <x:v>842</x:v>
+        <x:v>1006</x:v>
       </x:c>
       <x:c r="U97" s="0">
-        <x:v>842</x:v>
+        <x:v>1005</x:v>
       </x:c>
       <x:c r="V97" s="0">
-        <x:v>2953</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="W97" s="0">
-        <x:v>2955</x:v>
+        <x:v>3519</x:v>
       </x:c>
       <x:c r="X97" s="0">
-        <x:v>2954</x:v>
+        <x:v>3518</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
